--- a/work/batch3/batch3-review.xlsx
+++ b/work/batch3/batch3-review.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maost\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\[01] Martin\[07] Claude Code\NS2-Spanish-Translation\work\batch3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAC43371-0EAB-4F0C-828C-B3D9721FBE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D39489-D37B-4D48-8481-F3AEA64F30FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F68C1CE3-8B39-4140-BEDA-CCEB6670DD70}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F68C1CE3-8B39-4140-BEDA-CCEB6670DD70}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4041" uniqueCount="2229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4709" uniqueCount="2256">
   <si>
     <t>Section</t>
   </si>
@@ -6730,6 +6730,87 @@
   </si>
   <si>
     <t>Flagged left</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Keep current</t>
+  </si>
+  <si>
+    <t>Use my Spanish</t>
+  </si>
+  <si>
+    <t>Asistir a los jugadores</t>
+  </si>
+  <si>
+    <t>Mina de Bilis</t>
+  </si>
+  <si>
+    <t>Bomba de Bilis</t>
+  </si>
+  <si>
+    <t>Muro de Huesos</t>
+  </si>
+  <si>
+    <t>Impulso</t>
+  </si>
+  <si>
+    <t>Helps distinguish it from regular jumps, also called "Salto". Will use this from now on.</t>
+  </si>
+  <si>
+    <t>Metabolización</t>
+  </si>
+  <si>
+    <t>Following the trend of translating abilities.</t>
+  </si>
+  <si>
+    <t>Metabolización Avanzada</t>
+  </si>
+  <si>
+    <t>Nodo de energía</t>
+  </si>
+  <si>
+    <t>Sobretensión</t>
+  </si>
+  <si>
+    <t>Exotrajes</t>
+  </si>
+  <si>
+    <t>Aquí puedes comprar Exotrajes.</t>
+  </si>
+  <si>
+    <t>Investigar Exotrajes</t>
+  </si>
+  <si>
+    <t>Nodo de recursos</t>
+  </si>
+  <si>
+    <t>Batería de Energía</t>
+  </si>
+  <si>
+    <t>Puede atacar con su mordida y rastrear enemigos con el parásito. Puede emboscar a los enemigos trepando por paredes y techos. Puede evolucionar impulso y Xenocide.</t>
+  </si>
+  <si>
+    <t>Brazos dobles de Exotraje</t>
+  </si>
+  <si>
+    <t>Permite al Exotraje montar un arma en cada brazo en lugar de una garra en uno de ellos.</t>
+  </si>
+  <si>
+    <t>Desbloquea los módulos de núcleo del Exotraje: propulsores, asiento eyectable y placas de armadura.</t>
+  </si>
+  <si>
+    <t>Brazos avanzados de Exotraje</t>
+  </si>
+  <si>
+    <t>Un golpe lento y pesado. Hace más del doble de daño si golpea a un Exotraje por la espalda, salvo que tenga nano-escudo.</t>
+  </si>
+  <si>
+    <t>Núcleos de Exotraje</t>
+  </si>
+  <si>
+    <t>Permite a los Gorges lanzar un proyectil de asedio que hace daño en área a las estructuras y a la armadura de Marines y Exotrajes.</t>
   </si>
 </sst>
 </file>
@@ -7290,7 +7371,7 @@
       </c>
       <c r="B10" s="14">
         <f>COUNTA(Review!J2:J642)</f>
-        <v>0</v>
+        <v>641</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -7299,7 +7380,7 @@
       </c>
       <c r="B11" s="14">
         <f>ROWS(Review!J2:J642)-COUNTA(Review!J2:J642)</f>
-        <v>641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -7308,7 +7389,7 @@
       </c>
       <c r="B12" s="14">
         <f>COUNTIFS(Review!G2:G642,"?*",Review!J2:J642,"")</f>
-        <v>145</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7335,7 +7416,7 @@
     <col min="12" max="12" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7399,7 +7480,9 @@
         <v>19</v>
       </c>
       <c r="I2" s="4"/>
-      <c r="J2" s="7"/>
+      <c r="J2" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
     </row>
@@ -7425,7 +7508,9 @@
         <v>24</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="7"/>
+      <c r="J3" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
     </row>
@@ -7455,7 +7540,9 @@
         <v>29</v>
       </c>
       <c r="I4" s="4"/>
-      <c r="J4" s="7"/>
+      <c r="J4" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
     </row>
@@ -7481,7 +7568,9 @@
       <c r="G5" s="3"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
-      <c r="J5" s="7"/>
+      <c r="J5" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
     </row>
@@ -7507,7 +7596,9 @@
         <v>36</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="7"/>
+      <c r="J6" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
     </row>
@@ -7537,7 +7628,9 @@
         <v>41</v>
       </c>
       <c r="I7" s="4"/>
-      <c r="J7" s="7"/>
+      <c r="J7" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
     </row>
@@ -7567,7 +7660,9 @@
         <v>46</v>
       </c>
       <c r="I8" s="4"/>
-      <c r="J8" s="7"/>
+      <c r="J8" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
@@ -7597,7 +7692,9 @@
         <v>51</v>
       </c>
       <c r="I9" s="4"/>
-      <c r="J9" s="7"/>
+      <c r="J9" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
     </row>
@@ -7621,7 +7718,9 @@
       <c r="G10" s="3"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
-      <c r="J10" s="7"/>
+      <c r="J10" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
     </row>
@@ -7647,7 +7746,9 @@
       <c r="G11" s="3"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
-      <c r="J11" s="7"/>
+      <c r="J11" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
     </row>
@@ -7673,7 +7774,9 @@
       <c r="G12" s="3"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="7"/>
+      <c r="J12" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
     </row>
@@ -7699,7 +7802,9 @@
       <c r="G13" s="3"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="7"/>
+      <c r="J13" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
     </row>
@@ -7729,7 +7834,9 @@
         <v>69</v>
       </c>
       <c r="I14" s="4"/>
-      <c r="J14" s="7"/>
+      <c r="J14" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
     </row>
@@ -7755,7 +7862,9 @@
       <c r="G15" s="3"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
-      <c r="J15" s="7"/>
+      <c r="J15" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
     </row>
@@ -7781,7 +7890,9 @@
       <c r="G16" s="3"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="7"/>
+      <c r="J16" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
     </row>
@@ -7807,7 +7918,9 @@
       <c r="G17" s="3"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="7"/>
+      <c r="J17" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
     </row>
@@ -7833,7 +7946,9 @@
       <c r="G18" s="3"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="7"/>
+      <c r="J18" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
@@ -7859,7 +7974,9 @@
       <c r="G19" s="3"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="7"/>
+      <c r="J19" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
     </row>
@@ -7887,7 +8004,9 @@
         <v>88</v>
       </c>
       <c r="I20" s="4"/>
-      <c r="J20" s="7"/>
+      <c r="J20" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
     </row>
@@ -7913,7 +8032,9 @@
       <c r="G21" s="3"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="7"/>
+      <c r="J21" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
     </row>
@@ -7943,7 +8064,9 @@
         <v>96</v>
       </c>
       <c r="I22" s="4"/>
-      <c r="J22" s="7"/>
+      <c r="J22" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
     </row>
@@ -7973,7 +8096,9 @@
         <v>101</v>
       </c>
       <c r="I23" s="4"/>
-      <c r="J23" s="7"/>
+      <c r="J23" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
     </row>
@@ -8003,7 +8128,9 @@
         <v>106</v>
       </c>
       <c r="I24" s="4"/>
-      <c r="J24" s="7"/>
+      <c r="J24" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
     </row>
@@ -8027,7 +8154,9 @@
       <c r="G25" s="3"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="7"/>
+      <c r="J25" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
     </row>
@@ -8053,7 +8182,9 @@
       <c r="G26" s="3"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="7"/>
+      <c r="J26" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
     </row>
@@ -8079,7 +8210,9 @@
       <c r="G27" s="3"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="7"/>
+      <c r="J27" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
     </row>
@@ -8109,7 +8242,9 @@
         <v>120</v>
       </c>
       <c r="I28" s="4"/>
-      <c r="J28" s="7"/>
+      <c r="J28" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
     </row>
@@ -8135,7 +8270,9 @@
       <c r="G29" s="3"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
-      <c r="J29" s="7"/>
+      <c r="J29" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
     </row>
@@ -8161,7 +8298,9 @@
       <c r="G30" s="3"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="7"/>
+      <c r="J30" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
     </row>
@@ -8191,7 +8330,9 @@
         <v>130</v>
       </c>
       <c r="I31" s="4"/>
-      <c r="J31" s="7"/>
+      <c r="J31" s="7" t="s">
+        <v>2230</v>
+      </c>
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
     </row>
@@ -8219,7 +8360,9 @@
       <c r="I32" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="J32" s="7"/>
+      <c r="J32" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
     </row>
@@ -8243,7 +8386,9 @@
       <c r="G33" s="3"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
-      <c r="J33" s="7"/>
+      <c r="J33" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
     </row>
@@ -8269,7 +8414,9 @@
       <c r="G34" s="3"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="7"/>
+      <c r="J34" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
     </row>
@@ -8297,7 +8444,9 @@
         <v>142</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" s="7"/>
+      <c r="J35" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
     </row>
@@ -8323,7 +8472,9 @@
       <c r="G36" s="3"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
-      <c r="J36" s="7"/>
+      <c r="J36" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
     </row>
@@ -8349,7 +8500,9 @@
       <c r="G37" s="3"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
-      <c r="J37" s="7"/>
+      <c r="J37" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
     </row>
@@ -8375,7 +8528,9 @@
         <v>152</v>
       </c>
       <c r="I38" s="4"/>
-      <c r="J38" s="7"/>
+      <c r="J38" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
     </row>
@@ -8405,7 +8560,9 @@
         <v>157</v>
       </c>
       <c r="I39" s="4"/>
-      <c r="J39" s="7"/>
+      <c r="J39" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
     </row>
@@ -8431,7 +8588,9 @@
       <c r="G40" s="3"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
-      <c r="J40" s="7"/>
+      <c r="J40" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
     </row>
@@ -8461,7 +8620,9 @@
         <v>166</v>
       </c>
       <c r="I41" s="4"/>
-      <c r="J41" s="7"/>
+      <c r="J41" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K41" s="8"/>
       <c r="L41" s="8"/>
     </row>
@@ -8485,7 +8646,9 @@
       <c r="G42" s="3"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
-      <c r="J42" s="7"/>
+      <c r="J42" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
     </row>
@@ -8509,7 +8672,9 @@
       <c r="G43" s="3"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
-      <c r="J43" s="7"/>
+      <c r="J43" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K43" s="8"/>
       <c r="L43" s="8"/>
     </row>
@@ -8535,7 +8700,9 @@
       <c r="G44" s="3"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
-      <c r="J44" s="7"/>
+      <c r="J44" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K44" s="8"/>
       <c r="L44" s="8"/>
     </row>
@@ -8561,7 +8728,9 @@
       <c r="G45" s="3"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
-      <c r="J45" s="7"/>
+      <c r="J45" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
     </row>
@@ -8587,7 +8756,9 @@
       <c r="G46" s="3"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
-      <c r="J46" s="7"/>
+      <c r="J46" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
     </row>
@@ -8611,7 +8782,9 @@
       <c r="G47" s="3"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
-      <c r="J47" s="7"/>
+      <c r="J47" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
     </row>
@@ -8637,7 +8810,9 @@
       <c r="G48" s="3"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
-      <c r="J48" s="7"/>
+      <c r="J48" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K48" s="8"/>
       <c r="L48" s="8"/>
     </row>
@@ -8665,7 +8840,9 @@
         <v>193</v>
       </c>
       <c r="I49" s="4"/>
-      <c r="J49" s="7"/>
+      <c r="J49" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K49" s="8"/>
       <c r="L49" s="8"/>
     </row>
@@ -8691,7 +8868,9 @@
       <c r="G50" s="3"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
-      <c r="J50" s="7"/>
+      <c r="J50" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
     </row>
@@ -8715,7 +8894,9 @@
       <c r="G51" s="3"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
-      <c r="J51" s="7"/>
+      <c r="J51" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
     </row>
@@ -8741,7 +8922,9 @@
       <c r="G52" s="3"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-      <c r="J52" s="7"/>
+      <c r="J52" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
     </row>
@@ -8767,7 +8950,9 @@
       <c r="G53" s="3"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
-      <c r="J53" s="7"/>
+      <c r="J53" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
     </row>
@@ -8793,8 +8978,12 @@
       <c r="G54" s="3"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="8"/>
+      <c r="J54" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>2232</v>
+      </c>
       <c r="L54" s="8"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
@@ -8819,7 +9008,9 @@
       <c r="G55" s="3"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
-      <c r="J55" s="7"/>
+      <c r="J55" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
     </row>
@@ -8845,7 +9036,9 @@
       <c r="G56" s="3"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
-      <c r="J56" s="7"/>
+      <c r="J56" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K56" s="8"/>
       <c r="L56" s="8"/>
     </row>
@@ -8871,7 +9064,9 @@
         <v>24</v>
       </c>
       <c r="I57" s="4"/>
-      <c r="J57" s="7"/>
+      <c r="J57" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K57" s="8"/>
       <c r="L57" s="8"/>
     </row>
@@ -8895,7 +9090,9 @@
       <c r="G58" s="3"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="J58" s="7"/>
+      <c r="J58" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K58" s="8"/>
       <c r="L58" s="8"/>
     </row>
@@ -8923,7 +9120,9 @@
         <v>226</v>
       </c>
       <c r="I59" s="4"/>
-      <c r="J59" s="7"/>
+      <c r="J59" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K59" s="8"/>
       <c r="L59" s="8"/>
     </row>
@@ -8947,7 +9146,9 @@
       <c r="G60" s="3"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
-      <c r="J60" s="7"/>
+      <c r="J60" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
     </row>
@@ -8973,7 +9174,9 @@
       <c r="G61" s="3"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
-      <c r="J61" s="7"/>
+      <c r="J61" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K61" s="8"/>
       <c r="L61" s="8"/>
     </row>
@@ -9003,7 +9206,9 @@
         <v>237</v>
       </c>
       <c r="I62" s="4"/>
-      <c r="J62" s="7"/>
+      <c r="J62" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K62" s="8"/>
       <c r="L62" s="8"/>
     </row>
@@ -9033,8 +9238,12 @@
       <c r="I63" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="J63" s="7"/>
-      <c r="K63" s="8"/>
+      <c r="J63" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>2233</v>
+      </c>
       <c r="L63" s="8"/>
     </row>
     <row r="64" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
@@ -9057,7 +9266,9 @@
       <c r="G64" s="3"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
-      <c r="J64" s="7"/>
+      <c r="J64" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K64" s="8"/>
       <c r="L64" s="8"/>
     </row>
@@ -9087,7 +9298,9 @@
         <v>250</v>
       </c>
       <c r="I65" s="4"/>
-      <c r="J65" s="7"/>
+      <c r="J65" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K65" s="8"/>
       <c r="L65" s="8"/>
     </row>
@@ -9115,7 +9328,9 @@
         <v>255</v>
       </c>
       <c r="I66" s="4"/>
-      <c r="J66" s="7"/>
+      <c r="J66" s="7" t="s">
+        <v>2230</v>
+      </c>
       <c r="K66" s="8"/>
       <c r="L66" s="8"/>
     </row>
@@ -9143,7 +9358,9 @@
         <v>259</v>
       </c>
       <c r="I67" s="4"/>
-      <c r="J67" s="7"/>
+      <c r="J67" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K67" s="8"/>
       <c r="L67" s="8"/>
     </row>
@@ -9169,7 +9386,9 @@
       <c r="G68" s="3"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
-      <c r="J68" s="7"/>
+      <c r="J68" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K68" s="8"/>
       <c r="L68" s="8"/>
     </row>
@@ -9195,8 +9414,12 @@
         <v>266</v>
       </c>
       <c r="I69" s="4"/>
-      <c r="J69" s="7"/>
-      <c r="K69" s="8"/>
+      <c r="J69" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K69" s="8" t="s">
+        <v>2234</v>
+      </c>
       <c r="L69" s="8"/>
     </row>
     <row r="70" spans="1:12" ht="51" x14ac:dyDescent="0.2">
@@ -9225,8 +9448,12 @@
         <v>271</v>
       </c>
       <c r="I70" s="4"/>
-      <c r="J70" s="7"/>
-      <c r="K70" s="8"/>
+      <c r="J70" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K70" s="8" t="s">
+        <v>2255</v>
+      </c>
       <c r="L70" s="8"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
@@ -9253,7 +9480,9 @@
         <v>24</v>
       </c>
       <c r="I71" s="4"/>
-      <c r="J71" s="7"/>
+      <c r="J71" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K71" s="8"/>
       <c r="L71" s="8"/>
     </row>
@@ -9277,7 +9506,9 @@
       <c r="G72" s="3"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
-      <c r="J72" s="7"/>
+      <c r="J72" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K72" s="8"/>
       <c r="L72" s="8"/>
     </row>
@@ -9307,7 +9538,9 @@
         <v>282</v>
       </c>
       <c r="I73" s="4"/>
-      <c r="J73" s="7"/>
+      <c r="J73" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K73" s="8"/>
       <c r="L73" s="8"/>
     </row>
@@ -9335,7 +9568,9 @@
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
-      <c r="J74" s="7"/>
+      <c r="J74" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K74" s="8"/>
       <c r="L74" s="8"/>
     </row>
@@ -9363,7 +9598,9 @@
       </c>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
-      <c r="J75" s="7"/>
+      <c r="J75" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K75" s="8"/>
       <c r="L75" s="8"/>
     </row>
@@ -9391,7 +9628,9 @@
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
-      <c r="J76" s="7"/>
+      <c r="J76" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K76" s="8"/>
       <c r="L76" s="8"/>
     </row>
@@ -9419,7 +9658,9 @@
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
-      <c r="J77" s="7"/>
+      <c r="J77" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K77" s="8"/>
       <c r="L77" s="8"/>
     </row>
@@ -9447,7 +9688,9 @@
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
-      <c r="J78" s="7"/>
+      <c r="J78" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K78" s="8"/>
       <c r="L78" s="8"/>
     </row>
@@ -9475,7 +9718,9 @@
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
-      <c r="J79" s="7"/>
+      <c r="J79" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K79" s="8"/>
       <c r="L79" s="8"/>
     </row>
@@ -9499,7 +9744,9 @@
       <c r="G80" s="3"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
-      <c r="J80" s="7"/>
+      <c r="J80" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K80" s="8"/>
       <c r="L80" s="8"/>
     </row>
@@ -9527,7 +9774,9 @@
       </c>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
-      <c r="J81" s="7"/>
+      <c r="J81" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K81" s="8"/>
       <c r="L81" s="8"/>
     </row>
@@ -9551,7 +9800,9 @@
       <c r="G82" s="3"/>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
-      <c r="J82" s="7"/>
+      <c r="J82" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K82" s="8"/>
       <c r="L82" s="8"/>
     </row>
@@ -9579,7 +9830,9 @@
       </c>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
-      <c r="J83" s="7"/>
+      <c r="J83" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K83" s="8"/>
       <c r="L83" s="8"/>
     </row>
@@ -9605,7 +9858,9 @@
         <v>24</v>
       </c>
       <c r="I84" s="4"/>
-      <c r="J84" s="7"/>
+      <c r="J84" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K84" s="8"/>
       <c r="L84" s="8"/>
     </row>
@@ -9635,7 +9890,9 @@
         <v>328</v>
       </c>
       <c r="I85" s="4"/>
-      <c r="J85" s="7"/>
+      <c r="J85" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K85" s="8"/>
       <c r="L85" s="8"/>
     </row>
@@ -9661,7 +9918,9 @@
         <v>266</v>
       </c>
       <c r="I86" s="4"/>
-      <c r="J86" s="7"/>
+      <c r="J86" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K86" s="8"/>
       <c r="L86" s="8"/>
     </row>
@@ -9687,7 +9946,9 @@
       <c r="G87" s="3"/>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
-      <c r="J87" s="7"/>
+      <c r="J87" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K87" s="8"/>
       <c r="L87" s="8"/>
     </row>
@@ -9715,7 +9976,9 @@
         <v>337</v>
       </c>
       <c r="I88" s="4"/>
-      <c r="J88" s="7"/>
+      <c r="J88" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K88" s="8"/>
       <c r="L88" s="8"/>
     </row>
@@ -9743,7 +10006,9 @@
         <v>342</v>
       </c>
       <c r="I89" s="4"/>
-      <c r="J89" s="7"/>
+      <c r="J89" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K89" s="8"/>
       <c r="L89" s="8"/>
     </row>
@@ -9769,7 +10034,9 @@
         <v>346</v>
       </c>
       <c r="I90" s="4"/>
-      <c r="J90" s="7"/>
+      <c r="J90" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K90" s="8"/>
       <c r="L90" s="8"/>
     </row>
@@ -9795,7 +10062,9 @@
       <c r="G91" s="3"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
-      <c r="J91" s="7"/>
+      <c r="J91" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K91" s="8"/>
       <c r="L91" s="8"/>
     </row>
@@ -9821,7 +10090,9 @@
       <c r="G92" s="3"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
-      <c r="J92" s="7"/>
+      <c r="J92" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K92" s="8"/>
       <c r="L92" s="8"/>
     </row>
@@ -9847,7 +10118,9 @@
       <c r="G93" s="3"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
-      <c r="J93" s="7"/>
+      <c r="J93" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K93" s="8"/>
       <c r="L93" s="8"/>
     </row>
@@ -9873,7 +10146,9 @@
       <c r="G94" s="3"/>
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
-      <c r="J94" s="7"/>
+      <c r="J94" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K94" s="8"/>
       <c r="L94" s="8"/>
     </row>
@@ -9899,7 +10174,9 @@
       <c r="G95" s="3"/>
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
-      <c r="J95" s="7"/>
+      <c r="J95" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K95" s="8"/>
       <c r="L95" s="8"/>
     </row>
@@ -9923,7 +10200,9 @@
       <c r="G96" s="3"/>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
-      <c r="J96" s="7"/>
+      <c r="J96" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K96" s="8"/>
       <c r="L96" s="8"/>
     </row>
@@ -9951,7 +10230,9 @@
         <v>367</v>
       </c>
       <c r="I97" s="4"/>
-      <c r="J97" s="7"/>
+      <c r="J97" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K97" s="8"/>
       <c r="L97" s="8"/>
     </row>
@@ -9977,7 +10258,9 @@
         <v>24</v>
       </c>
       <c r="I98" s="4"/>
-      <c r="J98" s="7"/>
+      <c r="J98" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K98" s="8"/>
       <c r="L98" s="8"/>
     </row>
@@ -10007,7 +10290,9 @@
         <v>375</v>
       </c>
       <c r="I99" s="4"/>
-      <c r="J99" s="7"/>
+      <c r="J99" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K99" s="8"/>
       <c r="L99" s="8"/>
     </row>
@@ -10033,7 +10318,9 @@
       <c r="G100" s="3"/>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
-      <c r="J100" s="7"/>
+      <c r="J100" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K100" s="8"/>
       <c r="L100" s="8"/>
     </row>
@@ -10059,8 +10346,12 @@
         <v>24</v>
       </c>
       <c r="I101" s="4"/>
-      <c r="J101" s="7"/>
-      <c r="K101" s="8"/>
+      <c r="J101" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K101" s="8" t="s">
+        <v>381</v>
+      </c>
       <c r="L101" s="8"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
@@ -10085,7 +10376,9 @@
       <c r="G102" s="3"/>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
-      <c r="J102" s="7"/>
+      <c r="J102" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K102" s="8"/>
       <c r="L102" s="8"/>
     </row>
@@ -10115,7 +10408,9 @@
         <v>388</v>
       </c>
       <c r="I103" s="4"/>
-      <c r="J103" s="7"/>
+      <c r="J103" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K103" s="8"/>
       <c r="L103" s="8"/>
     </row>
@@ -10139,7 +10434,9 @@
       <c r="G104" s="3"/>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
-      <c r="J104" s="7"/>
+      <c r="J104" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K104" s="8"/>
       <c r="L104" s="8"/>
     </row>
@@ -10165,7 +10462,9 @@
         <v>24</v>
       </c>
       <c r="I105" s="4"/>
-      <c r="J105" s="7"/>
+      <c r="J105" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K105" s="8"/>
       <c r="L105" s="8"/>
     </row>
@@ -10191,7 +10490,9 @@
       <c r="G106" s="3"/>
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
-      <c r="J106" s="7"/>
+      <c r="J106" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K106" s="8"/>
       <c r="L106" s="8"/>
     </row>
@@ -10221,7 +10522,9 @@
         <v>402</v>
       </c>
       <c r="I107" s="4"/>
-      <c r="J107" s="7"/>
+      <c r="J107" s="7" t="s">
+        <v>2230</v>
+      </c>
       <c r="K107" s="8"/>
       <c r="L107" s="8"/>
     </row>
@@ -10247,7 +10550,9 @@
       <c r="G108" s="3"/>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
-      <c r="J108" s="7"/>
+      <c r="J108" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K108" s="8"/>
       <c r="L108" s="8"/>
     </row>
@@ -10277,7 +10582,9 @@
         <v>410</v>
       </c>
       <c r="I109" s="4"/>
-      <c r="J109" s="7"/>
+      <c r="J109" s="7" t="s">
+        <v>2230</v>
+      </c>
       <c r="K109" s="8"/>
       <c r="L109" s="8"/>
     </row>
@@ -10307,7 +10614,9 @@
         <v>101</v>
       </c>
       <c r="I110" s="4"/>
-      <c r="J110" s="7"/>
+      <c r="J110" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K110" s="8"/>
       <c r="L110" s="8"/>
     </row>
@@ -10335,7 +10644,9 @@
         <v>418</v>
       </c>
       <c r="I111" s="4"/>
-      <c r="J111" s="7"/>
+      <c r="J111" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
     </row>
@@ -10359,7 +10670,9 @@
       <c r="G112" s="3"/>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
-      <c r="J112" s="7"/>
+      <c r="J112" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K112" s="8"/>
       <c r="L112" s="8"/>
     </row>
@@ -10389,7 +10702,9 @@
         <v>425</v>
       </c>
       <c r="I113" s="4"/>
-      <c r="J113" s="7"/>
+      <c r="J113" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K113" s="8"/>
       <c r="L113" s="8"/>
     </row>
@@ -10415,7 +10730,9 @@
       <c r="G114" s="3"/>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
-      <c r="J114" s="7"/>
+      <c r="J114" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K114" s="8"/>
       <c r="L114" s="8"/>
     </row>
@@ -10441,7 +10758,9 @@
       <c r="G115" s="3"/>
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
-      <c r="J115" s="7"/>
+      <c r="J115" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K115" s="8"/>
       <c r="L115" s="8"/>
     </row>
@@ -10471,7 +10790,9 @@
         <v>435</v>
       </c>
       <c r="I116" s="4"/>
-      <c r="J116" s="7"/>
+      <c r="J116" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K116" s="8"/>
       <c r="L116" s="8"/>
     </row>
@@ -10497,7 +10818,9 @@
       <c r="G117" s="3"/>
       <c r="H117" s="4"/>
       <c r="I117" s="4"/>
-      <c r="J117" s="7"/>
+      <c r="J117" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K117" s="8"/>
       <c r="L117" s="8"/>
     </row>
@@ -10523,7 +10846,9 @@
       <c r="G118" s="3"/>
       <c r="H118" s="4"/>
       <c r="I118" s="4"/>
-      <c r="J118" s="7"/>
+      <c r="J118" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K118" s="8"/>
       <c r="L118" s="8"/>
     </row>
@@ -10551,7 +10876,9 @@
       <c r="I119" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="J119" s="7"/>
+      <c r="J119" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K119" s="8"/>
       <c r="L119" s="8"/>
     </row>
@@ -10577,7 +10904,9 @@
       <c r="G120" s="3"/>
       <c r="H120" s="4"/>
       <c r="I120" s="4"/>
-      <c r="J120" s="7"/>
+      <c r="J120" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K120" s="8"/>
       <c r="L120" s="8"/>
     </row>
@@ -10605,7 +10934,9 @@
         <v>454</v>
       </c>
       <c r="I121" s="4"/>
-      <c r="J121" s="7"/>
+      <c r="J121" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K121" s="8"/>
       <c r="L121" s="8"/>
     </row>
@@ -10635,7 +10966,9 @@
         <v>459</v>
       </c>
       <c r="I122" s="4"/>
-      <c r="J122" s="7"/>
+      <c r="J122" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K122" s="8"/>
       <c r="L122" s="8"/>
     </row>
@@ -10659,7 +10992,9 @@
       <c r="G123" s="3"/>
       <c r="H123" s="4"/>
       <c r="I123" s="4"/>
-      <c r="J123" s="7"/>
+      <c r="J123" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K123" s="8"/>
       <c r="L123" s="8"/>
     </row>
@@ -10685,7 +11020,9 @@
       <c r="G124" s="3"/>
       <c r="H124" s="4"/>
       <c r="I124" s="4"/>
-      <c r="J124" s="7"/>
+      <c r="J124" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K124" s="8"/>
       <c r="L124" s="8"/>
     </row>
@@ -10713,7 +11050,9 @@
         <v>469</v>
       </c>
       <c r="I125" s="4"/>
-      <c r="J125" s="7"/>
+      <c r="J125" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K125" s="8"/>
       <c r="L125" s="8"/>
     </row>
@@ -10739,7 +11078,9 @@
       <c r="G126" s="3"/>
       <c r="H126" s="4"/>
       <c r="I126" s="4"/>
-      <c r="J126" s="7"/>
+      <c r="J126" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K126" s="8"/>
       <c r="L126" s="8"/>
     </row>
@@ -10767,7 +11108,9 @@
         <v>24</v>
       </c>
       <c r="I127" s="4"/>
-      <c r="J127" s="7"/>
+      <c r="J127" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K127" s="8"/>
       <c r="L127" s="8"/>
     </row>
@@ -10791,7 +11134,9 @@
       <c r="G128" s="3"/>
       <c r="H128" s="4"/>
       <c r="I128" s="4"/>
-      <c r="J128" s="7"/>
+      <c r="J128" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K128" s="8"/>
       <c r="L128" s="8"/>
     </row>
@@ -10815,7 +11160,9 @@
       <c r="G129" s="3"/>
       <c r="H129" s="4"/>
       <c r="I129" s="4"/>
-      <c r="J129" s="7"/>
+      <c r="J129" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K129" s="8"/>
       <c r="L129" s="8"/>
     </row>
@@ -10841,7 +11188,9 @@
       <c r="G130" s="3"/>
       <c r="H130" s="4"/>
       <c r="I130" s="4"/>
-      <c r="J130" s="7"/>
+      <c r="J130" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K130" s="8"/>
       <c r="L130" s="8"/>
     </row>
@@ -10867,7 +11216,9 @@
       <c r="G131" s="3"/>
       <c r="H131" s="4"/>
       <c r="I131" s="4"/>
-      <c r="J131" s="7"/>
+      <c r="J131" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K131" s="8"/>
       <c r="L131" s="8"/>
     </row>
@@ -10893,7 +11244,9 @@
       <c r="G132" s="3"/>
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
-      <c r="J132" s="7"/>
+      <c r="J132" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K132" s="8"/>
       <c r="L132" s="8"/>
     </row>
@@ -10919,7 +11272,9 @@
       <c r="G133" s="3"/>
       <c r="H133" s="4"/>
       <c r="I133" s="4"/>
-      <c r="J133" s="7"/>
+      <c r="J133" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K133" s="8"/>
       <c r="L133" s="8"/>
     </row>
@@ -10945,7 +11300,9 @@
       <c r="G134" s="3"/>
       <c r="H134" s="4"/>
       <c r="I134" s="4"/>
-      <c r="J134" s="7"/>
+      <c r="J134" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K134" s="8"/>
       <c r="L134" s="8"/>
     </row>
@@ -10971,7 +11328,9 @@
       <c r="G135" s="3"/>
       <c r="H135" s="4"/>
       <c r="I135" s="4"/>
-      <c r="J135" s="7"/>
+      <c r="J135" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K135" s="8"/>
       <c r="L135" s="8"/>
     </row>
@@ -10997,7 +11356,9 @@
       <c r="G136" s="3"/>
       <c r="H136" s="4"/>
       <c r="I136" s="4"/>
-      <c r="J136" s="7"/>
+      <c r="J136" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K136" s="8"/>
       <c r="L136" s="8"/>
     </row>
@@ -11023,7 +11384,9 @@
         <v>24</v>
       </c>
       <c r="I137" s="4"/>
-      <c r="J137" s="7"/>
+      <c r="J137" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K137" s="8"/>
       <c r="L137" s="8"/>
     </row>
@@ -11047,7 +11410,9 @@
       <c r="G138" s="3"/>
       <c r="H138" s="4"/>
       <c r="I138" s="4"/>
-      <c r="J138" s="7"/>
+      <c r="J138" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K138" s="8"/>
       <c r="L138" s="8"/>
     </row>
@@ -11071,7 +11436,9 @@
       <c r="G139" s="3"/>
       <c r="H139" s="4"/>
       <c r="I139" s="4"/>
-      <c r="J139" s="7"/>
+      <c r="J139" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K139" s="8"/>
       <c r="L139" s="8"/>
     </row>
@@ -11097,7 +11464,9 @@
         <v>516</v>
       </c>
       <c r="I140" s="4"/>
-      <c r="J140" s="7"/>
+      <c r="J140" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K140" s="8"/>
       <c r="L140" s="8"/>
     </row>
@@ -11121,7 +11490,9 @@
       <c r="G141" s="3"/>
       <c r="H141" s="4"/>
       <c r="I141" s="4"/>
-      <c r="J141" s="7"/>
+      <c r="J141" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K141" s="8"/>
       <c r="L141" s="8"/>
     </row>
@@ -11145,7 +11516,9 @@
       <c r="G142" s="3"/>
       <c r="H142" s="4"/>
       <c r="I142" s="4"/>
-      <c r="J142" s="7"/>
+      <c r="J142" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K142" s="8"/>
       <c r="L142" s="8"/>
     </row>
@@ -11169,7 +11542,9 @@
       <c r="G143" s="3"/>
       <c r="H143" s="4"/>
       <c r="I143" s="4"/>
-      <c r="J143" s="7"/>
+      <c r="J143" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K143" s="8"/>
       <c r="L143" s="8"/>
     </row>
@@ -11193,7 +11568,9 @@
       <c r="G144" s="3"/>
       <c r="H144" s="4"/>
       <c r="I144" s="4"/>
-      <c r="J144" s="7"/>
+      <c r="J144" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K144" s="8"/>
       <c r="L144" s="8"/>
     </row>
@@ -11217,7 +11594,9 @@
       <c r="G145" s="3"/>
       <c r="H145" s="4"/>
       <c r="I145" s="4"/>
-      <c r="J145" s="7"/>
+      <c r="J145" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K145" s="8"/>
       <c r="L145" s="8"/>
     </row>
@@ -11243,7 +11622,9 @@
       <c r="G146" s="3"/>
       <c r="H146" s="4"/>
       <c r="I146" s="4"/>
-      <c r="J146" s="7"/>
+      <c r="J146" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K146" s="8"/>
       <c r="L146" s="8"/>
     </row>
@@ -11271,7 +11652,9 @@
         <v>226</v>
       </c>
       <c r="I147" s="4"/>
-      <c r="J147" s="7"/>
+      <c r="J147" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K147" s="8"/>
       <c r="L147" s="8"/>
     </row>
@@ -11297,7 +11680,9 @@
       <c r="G148" s="3"/>
       <c r="H148" s="4"/>
       <c r="I148" s="4"/>
-      <c r="J148" s="7"/>
+      <c r="J148" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K148" s="8"/>
       <c r="L148" s="8"/>
     </row>
@@ -11323,7 +11708,9 @@
       <c r="G149" s="3"/>
       <c r="H149" s="4"/>
       <c r="I149" s="4"/>
-      <c r="J149" s="7"/>
+      <c r="J149" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K149" s="8"/>
       <c r="L149" s="8"/>
     </row>
@@ -11353,7 +11740,9 @@
         <v>550</v>
       </c>
       <c r="I150" s="4"/>
-      <c r="J150" s="7"/>
+      <c r="J150" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K150" s="8"/>
       <c r="L150" s="8"/>
     </row>
@@ -11377,7 +11766,9 @@
       <c r="G151" s="3"/>
       <c r="H151" s="4"/>
       <c r="I151" s="4"/>
-      <c r="J151" s="7"/>
+      <c r="J151" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K151" s="8"/>
       <c r="L151" s="8"/>
     </row>
@@ -11403,7 +11794,9 @@
       <c r="G152" s="3"/>
       <c r="H152" s="4"/>
       <c r="I152" s="4"/>
-      <c r="J152" s="7"/>
+      <c r="J152" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K152" s="8"/>
       <c r="L152" s="8"/>
     </row>
@@ -11431,7 +11824,9 @@
         <v>560</v>
       </c>
       <c r="I153" s="4"/>
-      <c r="J153" s="7"/>
+      <c r="J153" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K153" s="8"/>
       <c r="L153" s="8"/>
     </row>
@@ -11457,7 +11852,9 @@
         <v>24</v>
       </c>
       <c r="I154" s="4"/>
-      <c r="J154" s="7"/>
+      <c r="J154" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K154" s="8"/>
       <c r="L154" s="8"/>
     </row>
@@ -11483,7 +11880,9 @@
       <c r="G155" s="3"/>
       <c r="H155" s="4"/>
       <c r="I155" s="4"/>
-      <c r="J155" s="7"/>
+      <c r="J155" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K155" s="8"/>
       <c r="L155" s="8"/>
     </row>
@@ -11509,7 +11908,9 @@
       <c r="G156" s="3"/>
       <c r="H156" s="4"/>
       <c r="I156" s="4"/>
-      <c r="J156" s="7"/>
+      <c r="J156" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K156" s="8"/>
       <c r="L156" s="8"/>
     </row>
@@ -11535,7 +11936,9 @@
       <c r="G157" s="3"/>
       <c r="H157" s="4"/>
       <c r="I157" s="4"/>
-      <c r="J157" s="7"/>
+      <c r="J157" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K157" s="8"/>
       <c r="L157" s="8"/>
     </row>
@@ -11559,7 +11962,9 @@
       <c r="G158" s="3"/>
       <c r="H158" s="4"/>
       <c r="I158" s="4"/>
-      <c r="J158" s="7"/>
+      <c r="J158" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K158" s="8"/>
       <c r="L158" s="8"/>
     </row>
@@ -11583,7 +11988,9 @@
       <c r="G159" s="3"/>
       <c r="H159" s="4"/>
       <c r="I159" s="4"/>
-      <c r="J159" s="7"/>
+      <c r="J159" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K159" s="8"/>
       <c r="L159" s="8"/>
     </row>
@@ -11609,7 +12016,9 @@
       <c r="G160" s="3"/>
       <c r="H160" s="4"/>
       <c r="I160" s="4"/>
-      <c r="J160" s="7"/>
+      <c r="J160" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K160" s="8"/>
       <c r="L160" s="8"/>
     </row>
@@ -11633,7 +12042,9 @@
       <c r="G161" s="3"/>
       <c r="H161" s="4"/>
       <c r="I161" s="4"/>
-      <c r="J161" s="7"/>
+      <c r="J161" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K161" s="8"/>
       <c r="L161" s="8"/>
     </row>
@@ -11659,7 +12070,9 @@
       <c r="I162" s="10" t="s">
         <v>590</v>
       </c>
-      <c r="J162" s="7"/>
+      <c r="J162" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K162" s="8"/>
       <c r="L162" s="8"/>
     </row>
@@ -11683,7 +12096,9 @@
       <c r="G163" s="3"/>
       <c r="H163" s="4"/>
       <c r="I163" s="4"/>
-      <c r="J163" s="7"/>
+      <c r="J163" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K163" s="8"/>
       <c r="L163" s="8"/>
     </row>
@@ -11707,7 +12122,9 @@
       <c r="G164" s="3"/>
       <c r="H164" s="4"/>
       <c r="I164" s="4"/>
-      <c r="J164" s="7"/>
+      <c r="J164" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K164" s="8"/>
       <c r="L164" s="8"/>
     </row>
@@ -11733,7 +12150,9 @@
       <c r="G165" s="3"/>
       <c r="H165" s="4"/>
       <c r="I165" s="4"/>
-      <c r="J165" s="7"/>
+      <c r="J165" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K165" s="8"/>
       <c r="L165" s="8"/>
     </row>
@@ -11759,7 +12178,9 @@
       <c r="G166" s="3"/>
       <c r="H166" s="4"/>
       <c r="I166" s="4"/>
-      <c r="J166" s="7"/>
+      <c r="J166" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K166" s="8"/>
       <c r="L166" s="8"/>
     </row>
@@ -11789,7 +12210,9 @@
         <v>608</v>
       </c>
       <c r="I167" s="4"/>
-      <c r="J167" s="7"/>
+      <c r="J167" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K167" s="8"/>
       <c r="L167" s="8"/>
     </row>
@@ -11819,7 +12242,9 @@
         <v>613</v>
       </c>
       <c r="I168" s="4"/>
-      <c r="J168" s="7"/>
+      <c r="J168" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K168" s="8"/>
       <c r="L168" s="8"/>
     </row>
@@ -11845,7 +12270,9 @@
       <c r="G169" s="3"/>
       <c r="H169" s="4"/>
       <c r="I169" s="4"/>
-      <c r="J169" s="7"/>
+      <c r="J169" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K169" s="8"/>
       <c r="L169" s="8"/>
     </row>
@@ -11871,7 +12298,9 @@
         <v>24</v>
       </c>
       <c r="I170" s="4"/>
-      <c r="J170" s="7"/>
+      <c r="J170" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K170" s="8"/>
       <c r="L170" s="8"/>
     </row>
@@ -11897,7 +12326,9 @@
       <c r="G171" s="3"/>
       <c r="H171" s="4"/>
       <c r="I171" s="4"/>
-      <c r="J171" s="7"/>
+      <c r="J171" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K171" s="8"/>
       <c r="L171" s="8"/>
     </row>
@@ -11925,7 +12356,9 @@
         <v>627</v>
       </c>
       <c r="I172" s="4"/>
-      <c r="J172" s="7"/>
+      <c r="J172" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K172" s="8"/>
       <c r="L172" s="8"/>
     </row>
@@ -11951,7 +12384,9 @@
       <c r="G173" s="3"/>
       <c r="H173" s="4"/>
       <c r="I173" s="4"/>
-      <c r="J173" s="7"/>
+      <c r="J173" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K173" s="8"/>
       <c r="L173" s="8"/>
     </row>
@@ -11977,7 +12412,9 @@
       <c r="G174" s="3"/>
       <c r="H174" s="4"/>
       <c r="I174" s="4"/>
-      <c r="J174" s="7"/>
+      <c r="J174" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K174" s="8"/>
       <c r="L174" s="8"/>
     </row>
@@ -12003,7 +12440,9 @@
       <c r="G175" s="3"/>
       <c r="H175" s="4"/>
       <c r="I175" s="4"/>
-      <c r="J175" s="7"/>
+      <c r="J175" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K175" s="8"/>
       <c r="L175" s="8"/>
     </row>
@@ -12029,7 +12468,9 @@
       <c r="G176" s="3"/>
       <c r="H176" s="4"/>
       <c r="I176" s="4"/>
-      <c r="J176" s="7"/>
+      <c r="J176" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K176" s="8"/>
       <c r="L176" s="8"/>
     </row>
@@ -12055,7 +12496,9 @@
       <c r="G177" s="3"/>
       <c r="H177" s="4"/>
       <c r="I177" s="4"/>
-      <c r="J177" s="7"/>
+      <c r="J177" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K177" s="8"/>
       <c r="L177" s="8"/>
     </row>
@@ -12081,7 +12524,9 @@
       <c r="G178" s="3"/>
       <c r="H178" s="4"/>
       <c r="I178" s="4"/>
-      <c r="J178" s="7"/>
+      <c r="J178" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K178" s="8"/>
       <c r="L178" s="8"/>
     </row>
@@ -12107,7 +12552,9 @@
       <c r="G179" s="3"/>
       <c r="H179" s="4"/>
       <c r="I179" s="4"/>
-      <c r="J179" s="7"/>
+      <c r="J179" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K179" s="8"/>
       <c r="L179" s="8"/>
     </row>
@@ -12133,7 +12580,9 @@
       <c r="G180" s="3"/>
       <c r="H180" s="4"/>
       <c r="I180" s="4"/>
-      <c r="J180" s="7"/>
+      <c r="J180" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K180" s="8"/>
       <c r="L180" s="8"/>
     </row>
@@ -12159,7 +12608,9 @@
       <c r="G181" s="3"/>
       <c r="H181" s="4"/>
       <c r="I181" s="4"/>
-      <c r="J181" s="7"/>
+      <c r="J181" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K181" s="8"/>
       <c r="L181" s="8"/>
     </row>
@@ -12185,7 +12636,9 @@
       <c r="G182" s="3"/>
       <c r="H182" s="4"/>
       <c r="I182" s="4"/>
-      <c r="J182" s="7"/>
+      <c r="J182" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K182" s="8"/>
       <c r="L182" s="8"/>
     </row>
@@ -12211,7 +12664,9 @@
       <c r="G183" s="3"/>
       <c r="H183" s="4"/>
       <c r="I183" s="4"/>
-      <c r="J183" s="7"/>
+      <c r="J183" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K183" s="8"/>
       <c r="L183" s="8"/>
     </row>
@@ -12241,7 +12696,9 @@
         <v>666</v>
       </c>
       <c r="I184" s="4"/>
-      <c r="J184" s="7"/>
+      <c r="J184" s="7" t="s">
+        <v>2230</v>
+      </c>
       <c r="K184" s="8"/>
       <c r="L184" s="8"/>
     </row>
@@ -12267,7 +12724,9 @@
       <c r="G185" s="3"/>
       <c r="H185" s="4"/>
       <c r="I185" s="4"/>
-      <c r="J185" s="7"/>
+      <c r="J185" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K185" s="8"/>
       <c r="L185" s="8"/>
     </row>
@@ -12295,7 +12754,9 @@
         <v>673</v>
       </c>
       <c r="I186" s="4"/>
-      <c r="J186" s="7"/>
+      <c r="J186" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K186" s="8"/>
       <c r="L186" s="8"/>
     </row>
@@ -12321,7 +12782,9 @@
       <c r="G187" s="3"/>
       <c r="H187" s="4"/>
       <c r="I187" s="4"/>
-      <c r="J187" s="7"/>
+      <c r="J187" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K187" s="8"/>
       <c r="L187" s="8"/>
     </row>
@@ -12347,7 +12810,9 @@
       <c r="G188" s="3"/>
       <c r="H188" s="4"/>
       <c r="I188" s="4"/>
-      <c r="J188" s="7"/>
+      <c r="J188" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K188" s="8"/>
       <c r="L188" s="8"/>
     </row>
@@ -12373,7 +12838,9 @@
         <v>24</v>
       </c>
       <c r="I189" s="4"/>
-      <c r="J189" s="7"/>
+      <c r="J189" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K189" s="8"/>
       <c r="L189" s="8"/>
     </row>
@@ -12401,7 +12868,9 @@
         <v>685</v>
       </c>
       <c r="I190" s="4"/>
-      <c r="J190" s="7"/>
+      <c r="J190" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K190" s="8"/>
       <c r="L190" s="8"/>
     </row>
@@ -12427,7 +12896,9 @@
       <c r="G191" s="3"/>
       <c r="H191" s="4"/>
       <c r="I191" s="4"/>
-      <c r="J191" s="7"/>
+      <c r="J191" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K191" s="8"/>
       <c r="L191" s="8"/>
     </row>
@@ -12457,7 +12928,9 @@
         <v>694</v>
       </c>
       <c r="I192" s="4"/>
-      <c r="J192" s="7"/>
+      <c r="J192" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K192" s="8"/>
       <c r="L192" s="8"/>
     </row>
@@ -12481,7 +12954,9 @@
       <c r="G193" s="3"/>
       <c r="H193" s="4"/>
       <c r="I193" s="4"/>
-      <c r="J193" s="7"/>
+      <c r="J193" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K193" s="8"/>
       <c r="L193" s="8"/>
     </row>
@@ -12507,7 +12982,9 @@
       <c r="G194" s="3"/>
       <c r="H194" s="4"/>
       <c r="I194" s="4"/>
-      <c r="J194" s="7"/>
+      <c r="J194" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K194" s="8"/>
       <c r="L194" s="8"/>
     </row>
@@ -12539,7 +13016,9 @@
       <c r="I195" s="10" t="s">
         <v>705</v>
       </c>
-      <c r="J195" s="7"/>
+      <c r="J195" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K195" s="8"/>
       <c r="L195" s="8"/>
     </row>
@@ -12563,7 +13042,9 @@
       <c r="G196" s="3"/>
       <c r="H196" s="4"/>
       <c r="I196" s="4"/>
-      <c r="J196" s="7"/>
+      <c r="J196" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K196" s="8"/>
       <c r="L196" s="8"/>
     </row>
@@ -12589,7 +13070,9 @@
       <c r="G197" s="3"/>
       <c r="H197" s="4"/>
       <c r="I197" s="4"/>
-      <c r="J197" s="7"/>
+      <c r="J197" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K197" s="8"/>
       <c r="L197" s="8"/>
     </row>
@@ -12615,7 +13098,9 @@
       <c r="G198" s="3"/>
       <c r="H198" s="4"/>
       <c r="I198" s="4"/>
-      <c r="J198" s="7"/>
+      <c r="J198" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K198" s="8"/>
       <c r="L198" s="8"/>
     </row>
@@ -12639,7 +13124,9 @@
       <c r="G199" s="3"/>
       <c r="H199" s="4"/>
       <c r="I199" s="4"/>
-      <c r="J199" s="7"/>
+      <c r="J199" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K199" s="8"/>
       <c r="L199" s="8"/>
     </row>
@@ -12665,7 +13152,9 @@
       <c r="G200" s="3"/>
       <c r="H200" s="4"/>
       <c r="I200" s="4"/>
-      <c r="J200" s="7"/>
+      <c r="J200" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K200" s="8"/>
       <c r="L200" s="8"/>
     </row>
@@ -12693,7 +13182,9 @@
         <v>724</v>
       </c>
       <c r="I201" s="4"/>
-      <c r="J201" s="7"/>
+      <c r="J201" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K201" s="8"/>
       <c r="L201" s="8"/>
     </row>
@@ -12719,7 +13210,9 @@
       <c r="G202" s="3"/>
       <c r="H202" s="4"/>
       <c r="I202" s="4"/>
-      <c r="J202" s="7"/>
+      <c r="J202" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K202" s="8"/>
       <c r="L202" s="8"/>
     </row>
@@ -12745,7 +13238,9 @@
       <c r="G203" s="3"/>
       <c r="H203" s="4"/>
       <c r="I203" s="4"/>
-      <c r="J203" s="7"/>
+      <c r="J203" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K203" s="8"/>
       <c r="L203" s="8"/>
     </row>
@@ -12771,7 +13266,9 @@
         <v>24</v>
       </c>
       <c r="I204" s="4"/>
-      <c r="J204" s="7"/>
+      <c r="J204" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K204" s="8"/>
       <c r="L204" s="8"/>
     </row>
@@ -12795,7 +13292,9 @@
       <c r="G205" s="3"/>
       <c r="H205" s="4"/>
       <c r="I205" s="4"/>
-      <c r="J205" s="7"/>
+      <c r="J205" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K205" s="8"/>
       <c r="L205" s="8"/>
     </row>
@@ -12825,7 +13324,9 @@
         <v>743</v>
       </c>
       <c r="I206" s="4"/>
-      <c r="J206" s="7"/>
+      <c r="J206" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K206" s="8"/>
       <c r="L206" s="8"/>
     </row>
@@ -12851,7 +13352,9 @@
       <c r="G207" s="3"/>
       <c r="H207" s="4"/>
       <c r="I207" s="4"/>
-      <c r="J207" s="7"/>
+      <c r="J207" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K207" s="8"/>
       <c r="L207" s="8"/>
     </row>
@@ -12877,7 +13380,9 @@
       <c r="G208" s="3"/>
       <c r="H208" s="4"/>
       <c r="I208" s="4"/>
-      <c r="J208" s="7"/>
+      <c r="J208" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K208" s="8"/>
       <c r="L208" s="8"/>
     </row>
@@ -12903,7 +13408,9 @@
       <c r="G209" s="3"/>
       <c r="H209" s="4"/>
       <c r="I209" s="4"/>
-      <c r="J209" s="7"/>
+      <c r="J209" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K209" s="8"/>
       <c r="L209" s="8"/>
     </row>
@@ -12929,7 +13436,9 @@
       <c r="G210" s="3"/>
       <c r="H210" s="4"/>
       <c r="I210" s="4"/>
-      <c r="J210" s="7"/>
+      <c r="J210" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K210" s="8"/>
       <c r="L210" s="8"/>
     </row>
@@ -12955,7 +13464,9 @@
         <v>24</v>
       </c>
       <c r="I211" s="4"/>
-      <c r="J211" s="7"/>
+      <c r="J211" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K211" s="8"/>
       <c r="L211" s="8"/>
     </row>
@@ -12981,7 +13492,9 @@
       <c r="G212" s="3"/>
       <c r="H212" s="4"/>
       <c r="I212" s="4"/>
-      <c r="J212" s="7"/>
+      <c r="J212" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K212" s="8"/>
       <c r="L212" s="8"/>
     </row>
@@ -13005,7 +13518,9 @@
       <c r="G213" s="3"/>
       <c r="H213" s="4"/>
       <c r="I213" s="4"/>
-      <c r="J213" s="7"/>
+      <c r="J213" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K213" s="8"/>
       <c r="L213" s="8"/>
     </row>
@@ -13031,7 +13546,9 @@
       <c r="G214" s="3"/>
       <c r="H214" s="4"/>
       <c r="I214" s="4"/>
-      <c r="J214" s="7"/>
+      <c r="J214" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K214" s="8"/>
       <c r="L214" s="8"/>
     </row>
@@ -13057,7 +13574,9 @@
       <c r="G215" s="3"/>
       <c r="H215" s="4"/>
       <c r="I215" s="4"/>
-      <c r="J215" s="7"/>
+      <c r="J215" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K215" s="8"/>
       <c r="L215" s="8"/>
     </row>
@@ -13087,7 +13606,9 @@
         <v>778</v>
       </c>
       <c r="I216" s="4"/>
-      <c r="J216" s="7"/>
+      <c r="J216" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K216" s="8"/>
       <c r="L216" s="8"/>
     </row>
@@ -13113,7 +13634,9 @@
       <c r="G217" s="3"/>
       <c r="H217" s="4"/>
       <c r="I217" s="4"/>
-      <c r="J217" s="7"/>
+      <c r="J217" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K217" s="8"/>
       <c r="L217" s="8"/>
     </row>
@@ -13137,7 +13660,9 @@
       <c r="G218" s="3"/>
       <c r="H218" s="4"/>
       <c r="I218" s="4"/>
-      <c r="J218" s="7"/>
+      <c r="J218" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K218" s="8"/>
       <c r="L218" s="8"/>
     </row>
@@ -13165,7 +13690,9 @@
         <v>789</v>
       </c>
       <c r="I219" s="4"/>
-      <c r="J219" s="7"/>
+      <c r="J219" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K219" s="8"/>
       <c r="L219" s="8"/>
     </row>
@@ -13191,7 +13718,9 @@
       <c r="G220" s="3"/>
       <c r="H220" s="4"/>
       <c r="I220" s="4"/>
-      <c r="J220" s="7"/>
+      <c r="J220" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K220" s="8"/>
       <c r="L220" s="8"/>
     </row>
@@ -13221,7 +13750,9 @@
         <v>798</v>
       </c>
       <c r="I221" s="4"/>
-      <c r="J221" s="7"/>
+      <c r="J221" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K221" s="8"/>
       <c r="L221" s="8"/>
     </row>
@@ -13247,7 +13778,9 @@
       <c r="G222" s="3"/>
       <c r="H222" s="4"/>
       <c r="I222" s="4"/>
-      <c r="J222" s="7"/>
+      <c r="J222" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K222" s="8"/>
       <c r="L222" s="8"/>
     </row>
@@ -13273,7 +13806,9 @@
       <c r="G223" s="3"/>
       <c r="H223" s="4"/>
       <c r="I223" s="4"/>
-      <c r="J223" s="7"/>
+      <c r="J223" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K223" s="8"/>
       <c r="L223" s="8"/>
     </row>
@@ -13299,7 +13834,9 @@
       <c r="G224" s="3"/>
       <c r="H224" s="4"/>
       <c r="I224" s="4"/>
-      <c r="J224" s="7"/>
+      <c r="J224" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K224" s="8"/>
       <c r="L224" s="8"/>
     </row>
@@ -13325,7 +13862,9 @@
       <c r="G225" s="3"/>
       <c r="H225" s="4"/>
       <c r="I225" s="4"/>
-      <c r="J225" s="7"/>
+      <c r="J225" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K225" s="8"/>
       <c r="L225" s="8"/>
     </row>
@@ -13351,7 +13890,9 @@
       <c r="G226" s="3"/>
       <c r="H226" s="4"/>
       <c r="I226" s="4"/>
-      <c r="J226" s="7"/>
+      <c r="J226" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K226" s="8"/>
       <c r="L226" s="8"/>
     </row>
@@ -13377,7 +13918,9 @@
       <c r="G227" s="3"/>
       <c r="H227" s="4"/>
       <c r="I227" s="4"/>
-      <c r="J227" s="7"/>
+      <c r="J227" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K227" s="8"/>
       <c r="L227" s="8"/>
     </row>
@@ -13403,7 +13946,9 @@
       <c r="G228" s="3"/>
       <c r="H228" s="4"/>
       <c r="I228" s="4"/>
-      <c r="J228" s="7"/>
+      <c r="J228" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K228" s="8"/>
       <c r="L228" s="8"/>
     </row>
@@ -13429,7 +13974,9 @@
       <c r="G229" s="3"/>
       <c r="H229" s="4"/>
       <c r="I229" s="4"/>
-      <c r="J229" s="7"/>
+      <c r="J229" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K229" s="8"/>
       <c r="L229" s="8"/>
     </row>
@@ -13455,7 +14002,9 @@
       <c r="G230" s="3"/>
       <c r="H230" s="4"/>
       <c r="I230" s="4"/>
-      <c r="J230" s="7"/>
+      <c r="J230" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K230" s="8"/>
       <c r="L230" s="8"/>
     </row>
@@ -13481,7 +14030,9 @@
       <c r="G231" s="3"/>
       <c r="H231" s="4"/>
       <c r="I231" s="4"/>
-      <c r="J231" s="7"/>
+      <c r="J231" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K231" s="8"/>
       <c r="L231" s="8"/>
     </row>
@@ -13507,7 +14058,9 @@
       <c r="G232" s="3"/>
       <c r="H232" s="4"/>
       <c r="I232" s="4"/>
-      <c r="J232" s="7"/>
+      <c r="J232" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K232" s="8"/>
       <c r="L232" s="8"/>
     </row>
@@ -13533,7 +14086,9 @@
       <c r="G233" s="3"/>
       <c r="H233" s="4"/>
       <c r="I233" s="4"/>
-      <c r="J233" s="7"/>
+      <c r="J233" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K233" s="8"/>
       <c r="L233" s="8"/>
     </row>
@@ -13559,7 +14114,9 @@
       <c r="G234" s="3"/>
       <c r="H234" s="4"/>
       <c r="I234" s="4"/>
-      <c r="J234" s="7"/>
+      <c r="J234" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K234" s="8"/>
       <c r="L234" s="8"/>
     </row>
@@ -13585,7 +14142,9 @@
       <c r="G235" s="3"/>
       <c r="H235" s="4"/>
       <c r="I235" s="4"/>
-      <c r="J235" s="7"/>
+      <c r="J235" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K235" s="8"/>
       <c r="L235" s="8"/>
     </row>
@@ -13611,7 +14170,9 @@
       <c r="G236" s="3"/>
       <c r="H236" s="4"/>
       <c r="I236" s="4"/>
-      <c r="J236" s="7"/>
+      <c r="J236" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K236" s="8"/>
       <c r="L236" s="8"/>
     </row>
@@ -13637,7 +14198,9 @@
       <c r="G237" s="3"/>
       <c r="H237" s="4"/>
       <c r="I237" s="4"/>
-      <c r="J237" s="7"/>
+      <c r="J237" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K237" s="8"/>
       <c r="L237" s="8"/>
     </row>
@@ -13663,7 +14226,9 @@
       <c r="G238" s="3"/>
       <c r="H238" s="4"/>
       <c r="I238" s="4"/>
-      <c r="J238" s="7"/>
+      <c r="J238" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K238" s="8"/>
       <c r="L238" s="8"/>
     </row>
@@ -13689,7 +14254,9 @@
       <c r="G239" s="3"/>
       <c r="H239" s="4"/>
       <c r="I239" s="4"/>
-      <c r="J239" s="7"/>
+      <c r="J239" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K239" s="8"/>
       <c r="L239" s="8"/>
     </row>
@@ -13715,7 +14282,9 @@
       <c r="G240" s="3"/>
       <c r="H240" s="4"/>
       <c r="I240" s="4"/>
-      <c r="J240" s="7"/>
+      <c r="J240" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K240" s="8"/>
       <c r="L240" s="8"/>
     </row>
@@ -13741,7 +14310,9 @@
       <c r="G241" s="3"/>
       <c r="H241" s="4"/>
       <c r="I241" s="4"/>
-      <c r="J241" s="7"/>
+      <c r="J241" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K241" s="8"/>
       <c r="L241" s="8"/>
     </row>
@@ -13767,7 +14338,9 @@
       <c r="G242" s="3"/>
       <c r="H242" s="4"/>
       <c r="I242" s="4"/>
-      <c r="J242" s="7"/>
+      <c r="J242" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K242" s="8"/>
       <c r="L242" s="8"/>
     </row>
@@ -13797,7 +14370,9 @@
         <v>867</v>
       </c>
       <c r="I243" s="4"/>
-      <c r="J243" s="7"/>
+      <c r="J243" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K243" s="8"/>
       <c r="L243" s="8"/>
     </row>
@@ -13823,7 +14398,9 @@
       <c r="G244" s="3"/>
       <c r="H244" s="4"/>
       <c r="I244" s="4"/>
-      <c r="J244" s="7"/>
+      <c r="J244" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K244" s="8"/>
       <c r="L244" s="8"/>
     </row>
@@ -13849,7 +14426,9 @@
       <c r="G245" s="3"/>
       <c r="H245" s="4"/>
       <c r="I245" s="4"/>
-      <c r="J245" s="7"/>
+      <c r="J245" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K245" s="8"/>
       <c r="L245" s="8"/>
     </row>
@@ -13875,7 +14454,9 @@
       <c r="G246" s="3"/>
       <c r="H246" s="4"/>
       <c r="I246" s="4"/>
-      <c r="J246" s="7"/>
+      <c r="J246" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K246" s="8"/>
       <c r="L246" s="8"/>
     </row>
@@ -13901,7 +14482,9 @@
       <c r="G247" s="3"/>
       <c r="H247" s="4"/>
       <c r="I247" s="4"/>
-      <c r="J247" s="7"/>
+      <c r="J247" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K247" s="8"/>
       <c r="L247" s="8"/>
     </row>
@@ -13927,7 +14510,9 @@
       <c r="G248" s="3"/>
       <c r="H248" s="4"/>
       <c r="I248" s="4"/>
-      <c r="J248" s="7"/>
+      <c r="J248" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K248" s="8"/>
       <c r="L248" s="8"/>
     </row>
@@ -13953,7 +14538,9 @@
       <c r="G249" s="3"/>
       <c r="H249" s="4"/>
       <c r="I249" s="4"/>
-      <c r="J249" s="7"/>
+      <c r="J249" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K249" s="8"/>
       <c r="L249" s="8"/>
     </row>
@@ -13979,7 +14566,9 @@
       <c r="G250" s="3"/>
       <c r="H250" s="4"/>
       <c r="I250" s="4"/>
-      <c r="J250" s="7"/>
+      <c r="J250" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K250" s="8"/>
       <c r="L250" s="8"/>
     </row>
@@ -14005,7 +14594,9 @@
         <v>892</v>
       </c>
       <c r="I251" s="4"/>
-      <c r="J251" s="7"/>
+      <c r="J251" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K251" s="8"/>
       <c r="L251" s="8"/>
     </row>
@@ -14029,7 +14620,9 @@
       <c r="G252" s="3"/>
       <c r="H252" s="4"/>
       <c r="I252" s="4"/>
-      <c r="J252" s="7"/>
+      <c r="J252" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K252" s="8"/>
       <c r="L252" s="8"/>
     </row>
@@ -14053,7 +14646,9 @@
       <c r="G253" s="3"/>
       <c r="H253" s="4"/>
       <c r="I253" s="4"/>
-      <c r="J253" s="7"/>
+      <c r="J253" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K253" s="8"/>
       <c r="L253" s="8"/>
     </row>
@@ -14079,7 +14674,9 @@
       <c r="G254" s="3"/>
       <c r="H254" s="4"/>
       <c r="I254" s="4"/>
-      <c r="J254" s="7"/>
+      <c r="J254" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K254" s="8"/>
       <c r="L254" s="8"/>
     </row>
@@ -14105,7 +14702,9 @@
       <c r="G255" s="3"/>
       <c r="H255" s="4"/>
       <c r="I255" s="4"/>
-      <c r="J255" s="7"/>
+      <c r="J255" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K255" s="8"/>
       <c r="L255" s="8"/>
     </row>
@@ -14131,7 +14730,9 @@
         <v>906</v>
       </c>
       <c r="I256" s="4"/>
-      <c r="J256" s="7"/>
+      <c r="J256" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K256" s="8"/>
       <c r="L256" s="8"/>
     </row>
@@ -14159,7 +14760,9 @@
         <v>789</v>
       </c>
       <c r="I257" s="4"/>
-      <c r="J257" s="7"/>
+      <c r="J257" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K257" s="8"/>
       <c r="L257" s="8"/>
     </row>
@@ -14183,7 +14786,9 @@
       <c r="G258" s="3"/>
       <c r="H258" s="4"/>
       <c r="I258" s="4"/>
-      <c r="J258" s="7"/>
+      <c r="J258" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K258" s="8"/>
       <c r="L258" s="8"/>
     </row>
@@ -14211,7 +14816,9 @@
         <v>916</v>
       </c>
       <c r="I259" s="4"/>
-      <c r="J259" s="7"/>
+      <c r="J259" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K259" s="8"/>
       <c r="L259" s="8"/>
     </row>
@@ -14237,7 +14844,9 @@
       <c r="G260" s="3"/>
       <c r="H260" s="4"/>
       <c r="I260" s="4"/>
-      <c r="J260" s="7"/>
+      <c r="J260" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K260" s="8"/>
       <c r="L260" s="8"/>
     </row>
@@ -14265,7 +14874,9 @@
         <v>923</v>
       </c>
       <c r="I261" s="4"/>
-      <c r="J261" s="7"/>
+      <c r="J261" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K261" s="8"/>
       <c r="L261" s="8"/>
     </row>
@@ -14289,7 +14900,9 @@
       <c r="G262" s="3"/>
       <c r="H262" s="4"/>
       <c r="I262" s="4"/>
-      <c r="J262" s="7"/>
+      <c r="J262" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K262" s="8"/>
       <c r="L262" s="8"/>
     </row>
@@ -14313,7 +14926,9 @@
       <c r="G263" s="3"/>
       <c r="H263" s="4"/>
       <c r="I263" s="4"/>
-      <c r="J263" s="7"/>
+      <c r="J263" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K263" s="8"/>
       <c r="L263" s="8"/>
     </row>
@@ -14339,7 +14954,9 @@
       <c r="G264" s="3"/>
       <c r="H264" s="4"/>
       <c r="I264" s="4"/>
-      <c r="J264" s="7"/>
+      <c r="J264" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K264" s="8"/>
       <c r="L264" s="8"/>
     </row>
@@ -14365,7 +14982,9 @@
       <c r="G265" s="3"/>
       <c r="H265" s="4"/>
       <c r="I265" s="4"/>
-      <c r="J265" s="7"/>
+      <c r="J265" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K265" s="8"/>
       <c r="L265" s="8"/>
     </row>
@@ -14393,7 +15012,9 @@
         <v>939</v>
       </c>
       <c r="I266" s="4"/>
-      <c r="J266" s="7"/>
+      <c r="J266" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K266" s="8"/>
       <c r="L266" s="8"/>
     </row>
@@ -14419,7 +15040,9 @@
       <c r="G267" s="3"/>
       <c r="H267" s="4"/>
       <c r="I267" s="4"/>
-      <c r="J267" s="7"/>
+      <c r="J267" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K267" s="8"/>
       <c r="L267" s="8"/>
     </row>
@@ -14443,7 +15066,9 @@
       <c r="G268" s="3"/>
       <c r="H268" s="4"/>
       <c r="I268" s="4"/>
-      <c r="J268" s="7"/>
+      <c r="J268" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K268" s="8"/>
       <c r="L268" s="8"/>
     </row>
@@ -14469,7 +15094,9 @@
       <c r="G269" s="3"/>
       <c r="H269" s="4"/>
       <c r="I269" s="4"/>
-      <c r="J269" s="7"/>
+      <c r="J269" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K269" s="8"/>
       <c r="L269" s="8"/>
     </row>
@@ -14499,7 +15126,9 @@
         <v>952</v>
       </c>
       <c r="I270" s="4"/>
-      <c r="J270" s="7"/>
+      <c r="J270" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K270" s="8"/>
       <c r="L270" s="8"/>
     </row>
@@ -14523,7 +15152,9 @@
       <c r="G271" s="3"/>
       <c r="H271" s="4"/>
       <c r="I271" s="4"/>
-      <c r="J271" s="7"/>
+      <c r="J271" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K271" s="8"/>
       <c r="L271" s="8"/>
     </row>
@@ -14553,7 +15184,9 @@
         <v>959</v>
       </c>
       <c r="I272" s="4"/>
-      <c r="J272" s="7"/>
+      <c r="J272" s="7" t="s">
+        <v>2230</v>
+      </c>
       <c r="K272" s="8"/>
       <c r="L272" s="8"/>
     </row>
@@ -14583,7 +15216,9 @@
         <v>964</v>
       </c>
       <c r="I273" s="4"/>
-      <c r="J273" s="7"/>
+      <c r="J273" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K273" s="8"/>
       <c r="L273" s="8"/>
     </row>
@@ -14609,7 +15244,9 @@
       <c r="G274" s="3"/>
       <c r="H274" s="4"/>
       <c r="I274" s="4"/>
-      <c r="J274" s="7"/>
+      <c r="J274" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K274" s="8"/>
       <c r="L274" s="8"/>
     </row>
@@ -14635,8 +15272,12 @@
         <v>266</v>
       </c>
       <c r="I275" s="4"/>
-      <c r="J275" s="7"/>
-      <c r="K275" s="8"/>
+      <c r="J275" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K275" s="8" t="s">
+        <v>2235</v>
+      </c>
       <c r="L275" s="8"/>
     </row>
     <row r="276" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
@@ -14661,7 +15302,9 @@
       <c r="G276" s="3"/>
       <c r="H276" s="4"/>
       <c r="I276" s="4"/>
-      <c r="J276" s="7"/>
+      <c r="J276" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K276" s="8"/>
       <c r="L276" s="8"/>
     </row>
@@ -14687,7 +15330,9 @@
       <c r="G277" s="3"/>
       <c r="H277" s="4"/>
       <c r="I277" s="4"/>
-      <c r="J277" s="7"/>
+      <c r="J277" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K277" s="8"/>
       <c r="L277" s="8"/>
     </row>
@@ -14713,7 +15358,9 @@
         <v>980</v>
       </c>
       <c r="I278" s="4"/>
-      <c r="J278" s="7"/>
+      <c r="J278" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K278" s="8"/>
       <c r="L278" s="8"/>
     </row>
@@ -14737,7 +15384,9 @@
       <c r="G279" s="3"/>
       <c r="H279" s="4"/>
       <c r="I279" s="4"/>
-      <c r="J279" s="7"/>
+      <c r="J279" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K279" s="8"/>
       <c r="L279" s="8"/>
     </row>
@@ -14761,7 +15410,9 @@
       <c r="G280" s="3"/>
       <c r="H280" s="4"/>
       <c r="I280" s="4"/>
-      <c r="J280" s="7"/>
+      <c r="J280" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K280" s="8"/>
       <c r="L280" s="8"/>
     </row>
@@ -14789,7 +15440,9 @@
         <v>24</v>
       </c>
       <c r="I281" s="4"/>
-      <c r="J281" s="7"/>
+      <c r="J281" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K281" s="8"/>
       <c r="L281" s="8"/>
     </row>
@@ -14813,7 +15466,9 @@
       <c r="G282" s="3"/>
       <c r="H282" s="4"/>
       <c r="I282" s="4"/>
-      <c r="J282" s="7"/>
+      <c r="J282" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K282" s="8"/>
       <c r="L282" s="8"/>
     </row>
@@ -14841,7 +15496,9 @@
         <v>789</v>
       </c>
       <c r="I283" s="4"/>
-      <c r="J283" s="7"/>
+      <c r="J283" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K283" s="8"/>
       <c r="L283" s="8"/>
     </row>
@@ -14865,7 +15522,9 @@
       <c r="G284" s="3"/>
       <c r="H284" s="4"/>
       <c r="I284" s="4"/>
-      <c r="J284" s="7"/>
+      <c r="J284" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K284" s="8"/>
       <c r="L284" s="8"/>
     </row>
@@ -14889,7 +15548,9 @@
       <c r="G285" s="3"/>
       <c r="H285" s="4"/>
       <c r="I285" s="4"/>
-      <c r="J285" s="7"/>
+      <c r="J285" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K285" s="8"/>
       <c r="L285" s="8"/>
     </row>
@@ -14913,7 +15574,9 @@
       <c r="G286" s="3"/>
       <c r="H286" s="4"/>
       <c r="I286" s="4"/>
-      <c r="J286" s="7"/>
+      <c r="J286" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K286" s="8"/>
       <c r="L286" s="8"/>
     </row>
@@ -14937,7 +15600,9 @@
       <c r="G287" s="3"/>
       <c r="H287" s="4"/>
       <c r="I287" s="4"/>
-      <c r="J287" s="7"/>
+      <c r="J287" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K287" s="8"/>
       <c r="L287" s="8"/>
     </row>
@@ -14963,7 +15628,9 @@
       <c r="G288" s="3"/>
       <c r="H288" s="4"/>
       <c r="I288" s="4"/>
-      <c r="J288" s="7"/>
+      <c r="J288" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K288" s="8"/>
       <c r="L288" s="8"/>
     </row>
@@ -14993,7 +15660,9 @@
         <v>1014</v>
       </c>
       <c r="I289" s="4"/>
-      <c r="J289" s="7"/>
+      <c r="J289" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K289" s="8"/>
       <c r="L289" s="8"/>
     </row>
@@ -15023,11 +15692,13 @@
         <v>1019</v>
       </c>
       <c r="I290" s="4"/>
-      <c r="J290" s="7"/>
+      <c r="J290" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K290" s="8"/>
       <c r="L290" s="8"/>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A291" s="3" t="s">
         <v>12</v>
       </c>
@@ -15049,9 +15720,15 @@
         <v>24</v>
       </c>
       <c r="I291" s="4"/>
-      <c r="J291" s="7"/>
-      <c r="K291" s="8"/>
-      <c r="L291" s="8"/>
+      <c r="J291" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K291" s="8" t="s">
+        <v>2236</v>
+      </c>
+      <c r="L291" s="8" t="s">
+        <v>2237</v>
+      </c>
     </row>
     <row r="292" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A292" s="3" t="s">
@@ -15079,7 +15756,9 @@
         <v>1027</v>
       </c>
       <c r="I292" s="4"/>
-      <c r="J292" s="7"/>
+      <c r="J292" s="7" t="s">
+        <v>2230</v>
+      </c>
       <c r="K292" s="8"/>
       <c r="L292" s="8"/>
     </row>
@@ -15103,7 +15782,9 @@
       <c r="G293" s="3"/>
       <c r="H293" s="4"/>
       <c r="I293" s="4"/>
-      <c r="J293" s="7"/>
+      <c r="J293" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K293" s="8"/>
       <c r="L293" s="8"/>
     </row>
@@ -15129,7 +15810,9 @@
         <v>24</v>
       </c>
       <c r="I294" s="4"/>
-      <c r="J294" s="7"/>
+      <c r="J294" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K294" s="8"/>
       <c r="L294" s="8"/>
     </row>
@@ -15159,7 +15842,9 @@
         <v>1035</v>
       </c>
       <c r="I295" s="4"/>
-      <c r="J295" s="7"/>
+      <c r="J295" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K295" s="8"/>
       <c r="L295" s="8"/>
     </row>
@@ -15185,7 +15870,9 @@
       <c r="G296" s="3"/>
       <c r="H296" s="4"/>
       <c r="I296" s="4"/>
-      <c r="J296" s="7"/>
+      <c r="J296" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K296" s="8"/>
       <c r="L296" s="8"/>
     </row>
@@ -15211,7 +15898,9 @@
       <c r="G297" s="3"/>
       <c r="H297" s="4"/>
       <c r="I297" s="4"/>
-      <c r="J297" s="7"/>
+      <c r="J297" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K297" s="8"/>
       <c r="L297" s="8"/>
     </row>
@@ -15241,7 +15930,9 @@
         <v>1047</v>
       </c>
       <c r="I298" s="4"/>
-      <c r="J298" s="7"/>
+      <c r="J298" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K298" s="8"/>
       <c r="L298" s="8"/>
     </row>
@@ -15267,7 +15958,9 @@
       <c r="G299" s="3"/>
       <c r="H299" s="4"/>
       <c r="I299" s="4"/>
-      <c r="J299" s="7"/>
+      <c r="J299" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K299" s="8"/>
       <c r="L299" s="8"/>
     </row>
@@ -15291,7 +15984,9 @@
       <c r="G300" s="3"/>
       <c r="H300" s="4"/>
       <c r="I300" s="4"/>
-      <c r="J300" s="7"/>
+      <c r="J300" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K300" s="8"/>
       <c r="L300" s="8"/>
     </row>
@@ -15315,7 +16010,9 @@
       <c r="G301" s="3"/>
       <c r="H301" s="4"/>
       <c r="I301" s="4"/>
-      <c r="J301" s="7"/>
+      <c r="J301" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K301" s="8"/>
       <c r="L301" s="8"/>
     </row>
@@ -15345,7 +16042,9 @@
         <v>1058</v>
       </c>
       <c r="I302" s="4"/>
-      <c r="J302" s="7"/>
+      <c r="J302" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K302" s="8"/>
       <c r="L302" s="8"/>
     </row>
@@ -15371,7 +16070,9 @@
       <c r="G303" s="3"/>
       <c r="H303" s="4"/>
       <c r="I303" s="4"/>
-      <c r="J303" s="7"/>
+      <c r="J303" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K303" s="8"/>
       <c r="L303" s="8"/>
     </row>
@@ -15401,7 +16102,9 @@
         <v>1067</v>
       </c>
       <c r="I304" s="4"/>
-      <c r="J304" s="7"/>
+      <c r="J304" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K304" s="8"/>
       <c r="L304" s="8"/>
     </row>
@@ -15431,7 +16134,9 @@
         <v>1072</v>
       </c>
       <c r="I305" s="4"/>
-      <c r="J305" s="7"/>
+      <c r="J305" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K305" s="8"/>
       <c r="L305" s="8"/>
     </row>
@@ -15459,7 +16164,9 @@
       <c r="I306" s="10" t="s">
         <v>1077</v>
       </c>
-      <c r="J306" s="7"/>
+      <c r="J306" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K306" s="8"/>
       <c r="L306" s="8"/>
     </row>
@@ -15485,7 +16192,9 @@
       <c r="G307" s="3"/>
       <c r="H307" s="4"/>
       <c r="I307" s="4"/>
-      <c r="J307" s="7"/>
+      <c r="J307" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K307" s="8"/>
       <c r="L307" s="8"/>
     </row>
@@ -15511,7 +16220,9 @@
       <c r="G308" s="3"/>
       <c r="H308" s="4"/>
       <c r="I308" s="4"/>
-      <c r="J308" s="7"/>
+      <c r="J308" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K308" s="8"/>
       <c r="L308" s="8"/>
     </row>
@@ -15537,7 +16248,9 @@
       <c r="G309" s="3"/>
       <c r="H309" s="4"/>
       <c r="I309" s="4"/>
-      <c r="J309" s="7"/>
+      <c r="J309" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K309" s="8"/>
       <c r="L309" s="8"/>
     </row>
@@ -15561,7 +16274,9 @@
       <c r="G310" s="3"/>
       <c r="H310" s="4"/>
       <c r="I310" s="4"/>
-      <c r="J310" s="7"/>
+      <c r="J310" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K310" s="8"/>
       <c r="L310" s="8"/>
     </row>
@@ -15587,7 +16302,9 @@
       <c r="G311" s="3"/>
       <c r="H311" s="4"/>
       <c r="I311" s="4"/>
-      <c r="J311" s="7"/>
+      <c r="J311" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K311" s="8"/>
       <c r="L311" s="8"/>
     </row>
@@ -15617,7 +16334,9 @@
         <v>1095</v>
       </c>
       <c r="I312" s="4"/>
-      <c r="J312" s="7"/>
+      <c r="J312" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K312" s="8"/>
       <c r="L312" s="8"/>
     </row>
@@ -15643,7 +16362,9 @@
       <c r="G313" s="3"/>
       <c r="H313" s="4"/>
       <c r="I313" s="4"/>
-      <c r="J313" s="7"/>
+      <c r="J313" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K313" s="8"/>
       <c r="L313" s="8"/>
     </row>
@@ -15669,7 +16390,9 @@
       <c r="G314" s="3"/>
       <c r="H314" s="4"/>
       <c r="I314" s="4"/>
-      <c r="J314" s="7"/>
+      <c r="J314" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K314" s="8"/>
       <c r="L314" s="8"/>
     </row>
@@ -15695,7 +16418,9 @@
       <c r="G315" s="3"/>
       <c r="H315" s="4"/>
       <c r="I315" s="4"/>
-      <c r="J315" s="7"/>
+      <c r="J315" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K315" s="8"/>
       <c r="L315" s="8"/>
     </row>
@@ -15721,7 +16446,9 @@
       <c r="G316" s="3"/>
       <c r="H316" s="4"/>
       <c r="I316" s="4"/>
-      <c r="J316" s="7"/>
+      <c r="J316" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K316" s="8"/>
       <c r="L316" s="8"/>
     </row>
@@ -15747,7 +16474,9 @@
       <c r="G317" s="3"/>
       <c r="H317" s="4"/>
       <c r="I317" s="4"/>
-      <c r="J317" s="7"/>
+      <c r="J317" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K317" s="8"/>
       <c r="L317" s="8"/>
     </row>
@@ -15773,7 +16502,9 @@
       <c r="G318" s="3"/>
       <c r="H318" s="4"/>
       <c r="I318" s="4"/>
-      <c r="J318" s="7"/>
+      <c r="J318" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K318" s="8"/>
       <c r="L318" s="8"/>
     </row>
@@ -15799,7 +16530,9 @@
       <c r="G319" s="3"/>
       <c r="H319" s="4"/>
       <c r="I319" s="4"/>
-      <c r="J319" s="7"/>
+      <c r="J319" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K319" s="8"/>
       <c r="L319" s="8"/>
     </row>
@@ -15825,7 +16558,9 @@
       <c r="G320" s="3"/>
       <c r="H320" s="4"/>
       <c r="I320" s="4"/>
-      <c r="J320" s="7"/>
+      <c r="J320" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K320" s="8"/>
       <c r="L320" s="8"/>
     </row>
@@ -15855,7 +16590,9 @@
         <v>1120</v>
       </c>
       <c r="I321" s="4"/>
-      <c r="J321" s="7"/>
+      <c r="J321" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K321" s="8"/>
       <c r="L321" s="8"/>
     </row>
@@ -15881,7 +16618,9 @@
       <c r="G322" s="3"/>
       <c r="H322" s="4"/>
       <c r="I322" s="4"/>
-      <c r="J322" s="7"/>
+      <c r="J322" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K322" s="8"/>
       <c r="L322" s="8"/>
     </row>
@@ -15905,7 +16644,9 @@
       <c r="G323" s="3"/>
       <c r="H323" s="4"/>
       <c r="I323" s="4"/>
-      <c r="J323" s="7"/>
+      <c r="J323" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K323" s="8"/>
       <c r="L323" s="8"/>
     </row>
@@ -15931,7 +16672,9 @@
       <c r="G324" s="3"/>
       <c r="H324" s="4"/>
       <c r="I324" s="4"/>
-      <c r="J324" s="7"/>
+      <c r="J324" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K324" s="8"/>
       <c r="L324" s="8"/>
     </row>
@@ -15957,7 +16700,9 @@
       <c r="G325" s="3"/>
       <c r="H325" s="4"/>
       <c r="I325" s="4"/>
-      <c r="J325" s="7"/>
+      <c r="J325" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K325" s="8"/>
       <c r="L325" s="8"/>
     </row>
@@ -15983,7 +16728,9 @@
       <c r="G326" s="3"/>
       <c r="H326" s="4"/>
       <c r="I326" s="4"/>
-      <c r="J326" s="7"/>
+      <c r="J326" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K326" s="8"/>
       <c r="L326" s="8"/>
     </row>
@@ -16013,7 +16760,9 @@
         <v>1136</v>
       </c>
       <c r="I327" s="4"/>
-      <c r="J327" s="7"/>
+      <c r="J327" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K327" s="8"/>
       <c r="L327" s="8"/>
     </row>
@@ -16043,7 +16792,9 @@
         <v>101</v>
       </c>
       <c r="I328" s="4"/>
-      <c r="J328" s="7"/>
+      <c r="J328" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K328" s="8"/>
       <c r="L328" s="8"/>
     </row>
@@ -16069,7 +16820,9 @@
       <c r="G329" s="3"/>
       <c r="H329" s="4"/>
       <c r="I329" s="4"/>
-      <c r="J329" s="7"/>
+      <c r="J329" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K329" s="8"/>
       <c r="L329" s="8"/>
     </row>
@@ -16095,7 +16848,9 @@
       <c r="G330" s="3"/>
       <c r="H330" s="4"/>
       <c r="I330" s="4"/>
-      <c r="J330" s="7"/>
+      <c r="J330" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K330" s="8"/>
       <c r="L330" s="8"/>
     </row>
@@ -16121,7 +16876,9 @@
       <c r="G331" s="3"/>
       <c r="H331" s="4"/>
       <c r="I331" s="4"/>
-      <c r="J331" s="7"/>
+      <c r="J331" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K331" s="8"/>
       <c r="L331" s="8"/>
     </row>
@@ -16147,7 +16904,9 @@
       <c r="G332" s="3"/>
       <c r="H332" s="4"/>
       <c r="I332" s="4"/>
-      <c r="J332" s="7"/>
+      <c r="J332" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K332" s="8"/>
       <c r="L332" s="8"/>
     </row>
@@ -16173,7 +16932,9 @@
       <c r="G333" s="3"/>
       <c r="H333" s="4"/>
       <c r="I333" s="4"/>
-      <c r="J333" s="7"/>
+      <c r="J333" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K333" s="8"/>
       <c r="L333" s="8"/>
     </row>
@@ -16199,7 +16960,9 @@
       <c r="G334" s="3"/>
       <c r="H334" s="4"/>
       <c r="I334" s="4"/>
-      <c r="J334" s="7"/>
+      <c r="J334" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K334" s="8"/>
       <c r="L334" s="8"/>
     </row>
@@ -16225,7 +16988,9 @@
       <c r="G335" s="3"/>
       <c r="H335" s="4"/>
       <c r="I335" s="4"/>
-      <c r="J335" s="7"/>
+      <c r="J335" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K335" s="8"/>
       <c r="L335" s="8"/>
     </row>
@@ -16251,7 +17016,9 @@
       <c r="G336" s="3"/>
       <c r="H336" s="4"/>
       <c r="I336" s="4"/>
-      <c r="J336" s="7"/>
+      <c r="J336" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K336" s="8"/>
       <c r="L336" s="8"/>
     </row>
@@ -16277,7 +17044,9 @@
       <c r="G337" s="3"/>
       <c r="H337" s="4"/>
       <c r="I337" s="4"/>
-      <c r="J337" s="7"/>
+      <c r="J337" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K337" s="8"/>
       <c r="L337" s="8"/>
     </row>
@@ -16303,7 +17072,9 @@
       <c r="G338" s="3"/>
       <c r="H338" s="4"/>
       <c r="I338" s="4"/>
-      <c r="J338" s="7"/>
+      <c r="J338" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K338" s="8"/>
       <c r="L338" s="8"/>
     </row>
@@ -16329,7 +17100,9 @@
       <c r="G339" s="3"/>
       <c r="H339" s="4"/>
       <c r="I339" s="4"/>
-      <c r="J339" s="7"/>
+      <c r="J339" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K339" s="8"/>
       <c r="L339" s="8"/>
     </row>
@@ -16355,7 +17128,9 @@
       <c r="G340" s="3"/>
       <c r="H340" s="4"/>
       <c r="I340" s="4"/>
-      <c r="J340" s="7"/>
+      <c r="J340" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K340" s="8"/>
       <c r="L340" s="8"/>
     </row>
@@ -16379,7 +17154,9 @@
       <c r="G341" s="3"/>
       <c r="H341" s="4"/>
       <c r="I341" s="4"/>
-      <c r="J341" s="7"/>
+      <c r="J341" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K341" s="8"/>
       <c r="L341" s="8"/>
     </row>
@@ -16405,7 +17182,9 @@
       <c r="G342" s="3"/>
       <c r="H342" s="4"/>
       <c r="I342" s="4"/>
-      <c r="J342" s="7"/>
+      <c r="J342" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K342" s="8"/>
       <c r="L342" s="8"/>
     </row>
@@ -16429,7 +17208,9 @@
       <c r="G343" s="3"/>
       <c r="H343" s="4"/>
       <c r="I343" s="4"/>
-      <c r="J343" s="7"/>
+      <c r="J343" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K343" s="8"/>
       <c r="L343" s="8"/>
     </row>
@@ -16455,7 +17236,9 @@
       <c r="G344" s="3"/>
       <c r="H344" s="4"/>
       <c r="I344" s="4"/>
-      <c r="J344" s="7"/>
+      <c r="J344" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K344" s="8"/>
       <c r="L344" s="8"/>
     </row>
@@ -16479,7 +17262,9 @@
       <c r="G345" s="3"/>
       <c r="H345" s="4"/>
       <c r="I345" s="4"/>
-      <c r="J345" s="7"/>
+      <c r="J345" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K345" s="8"/>
       <c r="L345" s="8"/>
     </row>
@@ -16505,7 +17290,9 @@
       <c r="G346" s="3"/>
       <c r="H346" s="4"/>
       <c r="I346" s="4"/>
-      <c r="J346" s="7"/>
+      <c r="J346" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K346" s="8"/>
       <c r="L346" s="8"/>
     </row>
@@ -16531,7 +17318,9 @@
       <c r="G347" s="3"/>
       <c r="H347" s="4"/>
       <c r="I347" s="4"/>
-      <c r="J347" s="7"/>
+      <c r="J347" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K347" s="8"/>
       <c r="L347" s="8"/>
     </row>
@@ -16561,7 +17350,9 @@
         <v>1200</v>
       </c>
       <c r="I348" s="4"/>
-      <c r="J348" s="7"/>
+      <c r="J348" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K348" s="8"/>
       <c r="L348" s="8"/>
     </row>
@@ -16587,11 +17378,13 @@
       <c r="G349" s="3"/>
       <c r="H349" s="4"/>
       <c r="I349" s="4"/>
-      <c r="J349" s="7"/>
+      <c r="J349" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K349" s="8"/>
       <c r="L349" s="8"/>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A350" s="3" t="s">
         <v>12</v>
       </c>
@@ -16613,9 +17406,15 @@
         <v>266</v>
       </c>
       <c r="I350" s="4"/>
-      <c r="J350" s="7"/>
-      <c r="K350" s="8"/>
-      <c r="L350" s="8"/>
+      <c r="J350" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K350" s="8" t="s">
+        <v>2238</v>
+      </c>
+      <c r="L350" s="8" t="s">
+        <v>2239</v>
+      </c>
     </row>
     <row r="351" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A351" s="3" t="s">
@@ -16643,9 +17442,15 @@
         <v>1209</v>
       </c>
       <c r="I351" s="4"/>
-      <c r="J351" s="7"/>
-      <c r="K351" s="8"/>
-      <c r="L351" s="8"/>
+      <c r="J351" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K351" s="8" t="s">
+        <v>2240</v>
+      </c>
+      <c r="L351" s="8" t="s">
+        <v>2239</v>
+      </c>
     </row>
     <row r="352" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A352" s="3" t="s">
@@ -16669,7 +17474,9 @@
       <c r="G352" s="3"/>
       <c r="H352" s="4"/>
       <c r="I352" s="4"/>
-      <c r="J352" s="7"/>
+      <c r="J352" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K352" s="8"/>
       <c r="L352" s="8"/>
     </row>
@@ -16695,7 +17502,9 @@
       <c r="G353" s="3"/>
       <c r="H353" s="4"/>
       <c r="I353" s="4"/>
-      <c r="J353" s="7"/>
+      <c r="J353" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K353" s="8"/>
       <c r="L353" s="8"/>
     </row>
@@ -16721,7 +17530,9 @@
         <v>24</v>
       </c>
       <c r="I354" s="4"/>
-      <c r="J354" s="7"/>
+      <c r="J354" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K354" s="8"/>
       <c r="L354" s="8"/>
     </row>
@@ -16749,7 +17560,9 @@
         <v>789</v>
       </c>
       <c r="I355" s="4"/>
-      <c r="J355" s="7"/>
+      <c r="J355" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K355" s="8"/>
       <c r="L355" s="8"/>
     </row>
@@ -16779,7 +17592,9 @@
         <v>1228</v>
       </c>
       <c r="I356" s="4"/>
-      <c r="J356" s="7"/>
+      <c r="J356" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K356" s="8"/>
       <c r="L356" s="8"/>
     </row>
@@ -16805,7 +17620,9 @@
       <c r="G357" s="3"/>
       <c r="H357" s="4"/>
       <c r="I357" s="4"/>
-      <c r="J357" s="7"/>
+      <c r="J357" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K357" s="8"/>
       <c r="L357" s="8"/>
     </row>
@@ -16835,7 +17652,9 @@
         <v>1236</v>
       </c>
       <c r="I358" s="4"/>
-      <c r="J358" s="7"/>
+      <c r="J358" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K358" s="8"/>
       <c r="L358" s="8"/>
     </row>
@@ -16859,7 +17678,9 @@
       <c r="G359" s="3"/>
       <c r="H359" s="4"/>
       <c r="I359" s="4"/>
-      <c r="J359" s="7"/>
+      <c r="J359" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K359" s="8"/>
       <c r="L359" s="8"/>
     </row>
@@ -16889,7 +17710,9 @@
         <v>1243</v>
       </c>
       <c r="I360" s="4"/>
-      <c r="J360" s="7"/>
+      <c r="J360" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K360" s="8"/>
       <c r="L360" s="8"/>
     </row>
@@ -16919,7 +17742,9 @@
         <v>1248</v>
       </c>
       <c r="I361" s="4"/>
-      <c r="J361" s="7"/>
+      <c r="J361" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K361" s="8"/>
       <c r="L361" s="8"/>
     </row>
@@ -16951,7 +17776,9 @@
       <c r="I362" s="10" t="s">
         <v>1254</v>
       </c>
-      <c r="J362" s="7"/>
+      <c r="J362" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K362" s="8"/>
       <c r="L362" s="8"/>
     </row>
@@ -16979,7 +17806,9 @@
         <v>24</v>
       </c>
       <c r="I363" s="4"/>
-      <c r="J363" s="7"/>
+      <c r="J363" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K363" s="8"/>
       <c r="L363" s="8"/>
     </row>
@@ -17009,7 +17838,9 @@
         <v>1262</v>
       </c>
       <c r="I364" s="4"/>
-      <c r="J364" s="7"/>
+      <c r="J364" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K364" s="8"/>
       <c r="L364" s="8"/>
     </row>
@@ -17035,7 +17866,9 @@
         <v>24</v>
       </c>
       <c r="I365" s="4"/>
-      <c r="J365" s="7"/>
+      <c r="J365" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K365" s="8"/>
       <c r="L365" s="8"/>
     </row>
@@ -17061,7 +17894,9 @@
       <c r="G366" s="3"/>
       <c r="H366" s="4"/>
       <c r="I366" s="4"/>
-      <c r="J366" s="7"/>
+      <c r="J366" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K366" s="8"/>
       <c r="L366" s="8"/>
     </row>
@@ -17091,7 +17926,9 @@
         <v>1274</v>
       </c>
       <c r="I367" s="4"/>
-      <c r="J367" s="7"/>
+      <c r="J367" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K367" s="8"/>
       <c r="L367" s="8"/>
     </row>
@@ -17121,7 +17958,9 @@
         <v>1279</v>
       </c>
       <c r="I368" s="4"/>
-      <c r="J368" s="7"/>
+      <c r="J368" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K368" s="8"/>
       <c r="L368" s="8"/>
     </row>
@@ -17151,7 +17990,9 @@
         <v>1284</v>
       </c>
       <c r="I369" s="4"/>
-      <c r="J369" s="7"/>
+      <c r="J369" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K369" s="8"/>
       <c r="L369" s="8"/>
     </row>
@@ -17175,7 +18016,9 @@
       <c r="G370" s="3"/>
       <c r="H370" s="4"/>
       <c r="I370" s="4"/>
-      <c r="J370" s="7"/>
+      <c r="J370" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K370" s="8"/>
       <c r="L370" s="8"/>
     </row>
@@ -17201,7 +18044,9 @@
       <c r="G371" s="3"/>
       <c r="H371" s="4"/>
       <c r="I371" s="4"/>
-      <c r="J371" s="7"/>
+      <c r="J371" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K371" s="8"/>
       <c r="L371" s="8"/>
     </row>
@@ -17227,7 +18072,9 @@
       <c r="G372" s="3"/>
       <c r="H372" s="4"/>
       <c r="I372" s="4"/>
-      <c r="J372" s="7"/>
+      <c r="J372" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K372" s="8"/>
       <c r="L372" s="8"/>
     </row>
@@ -17251,7 +18098,9 @@
       <c r="G373" s="3"/>
       <c r="H373" s="4"/>
       <c r="I373" s="4"/>
-      <c r="J373" s="7"/>
+      <c r="J373" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K373" s="8"/>
       <c r="L373" s="8"/>
     </row>
@@ -17277,7 +18126,9 @@
       <c r="G374" s="3"/>
       <c r="H374" s="4"/>
       <c r="I374" s="4"/>
-      <c r="J374" s="7"/>
+      <c r="J374" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K374" s="8"/>
       <c r="L374" s="8"/>
     </row>
@@ -17303,7 +18154,9 @@
       <c r="G375" s="3"/>
       <c r="H375" s="4"/>
       <c r="I375" s="4"/>
-      <c r="J375" s="7"/>
+      <c r="J375" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K375" s="8"/>
       <c r="L375" s="8"/>
     </row>
@@ -17333,7 +18186,9 @@
         <v>1307</v>
       </c>
       <c r="I376" s="4"/>
-      <c r="J376" s="7"/>
+      <c r="J376" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K376" s="8"/>
       <c r="L376" s="8"/>
     </row>
@@ -17359,7 +18214,9 @@
       <c r="G377" s="3"/>
       <c r="H377" s="4"/>
       <c r="I377" s="4"/>
-      <c r="J377" s="7"/>
+      <c r="J377" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K377" s="8"/>
       <c r="L377" s="8"/>
     </row>
@@ -17385,7 +18242,9 @@
       <c r="G378" s="3"/>
       <c r="H378" s="4"/>
       <c r="I378" s="4"/>
-      <c r="J378" s="7"/>
+      <c r="J378" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K378" s="8"/>
       <c r="L378" s="8"/>
     </row>
@@ -17411,7 +18270,9 @@
         <v>24</v>
       </c>
       <c r="I379" s="4"/>
-      <c r="J379" s="7"/>
+      <c r="J379" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K379" s="8"/>
       <c r="L379" s="8"/>
     </row>
@@ -17437,7 +18298,9 @@
       <c r="G380" s="3"/>
       <c r="H380" s="4"/>
       <c r="I380" s="4"/>
-      <c r="J380" s="7"/>
+      <c r="J380" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K380" s="8"/>
       <c r="L380" s="8"/>
     </row>
@@ -17467,7 +18330,9 @@
         <v>1324</v>
       </c>
       <c r="I381" s="4"/>
-      <c r="J381" s="7"/>
+      <c r="J381" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K381" s="8"/>
       <c r="L381" s="8"/>
     </row>
@@ -17493,7 +18358,9 @@
       <c r="G382" s="3"/>
       <c r="H382" s="4"/>
       <c r="I382" s="4"/>
-      <c r="J382" s="7"/>
+      <c r="J382" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K382" s="8"/>
       <c r="L382" s="8"/>
     </row>
@@ -17523,7 +18390,9 @@
         <v>1333</v>
       </c>
       <c r="I383" s="4"/>
-      <c r="J383" s="7"/>
+      <c r="J383" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K383" s="8"/>
       <c r="L383" s="8"/>
     </row>
@@ -17549,7 +18418,9 @@
       <c r="G384" s="3"/>
       <c r="H384" s="4"/>
       <c r="I384" s="4"/>
-      <c r="J384" s="7"/>
+      <c r="J384" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K384" s="8"/>
       <c r="L384" s="8"/>
     </row>
@@ -17575,7 +18446,9 @@
         <v>24</v>
       </c>
       <c r="I385" s="4"/>
-      <c r="J385" s="7"/>
+      <c r="J385" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K385" s="8"/>
       <c r="L385" s="8"/>
     </row>
@@ -17601,7 +18474,9 @@
       <c r="G386" s="3"/>
       <c r="H386" s="4"/>
       <c r="I386" s="4"/>
-      <c r="J386" s="7"/>
+      <c r="J386" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K386" s="8"/>
       <c r="L386" s="8"/>
     </row>
@@ -17631,7 +18506,9 @@
         <v>1348</v>
       </c>
       <c r="I387" s="4"/>
-      <c r="J387" s="7"/>
+      <c r="J387" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K387" s="8"/>
       <c r="L387" s="8"/>
     </row>
@@ -17657,7 +18534,9 @@
         <v>24</v>
       </c>
       <c r="I388" s="4"/>
-      <c r="J388" s="7"/>
+      <c r="J388" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K388" s="8"/>
       <c r="L388" s="8"/>
     </row>
@@ -17689,7 +18568,9 @@
       <c r="I389" s="10" t="s">
         <v>1356</v>
       </c>
-      <c r="J389" s="7"/>
+      <c r="J389" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K389" s="8"/>
       <c r="L389" s="8"/>
     </row>
@@ -17719,7 +18600,9 @@
         <v>1361</v>
       </c>
       <c r="I390" s="4"/>
-      <c r="J390" s="7"/>
+      <c r="J390" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K390" s="8"/>
       <c r="L390" s="8"/>
     </row>
@@ -17749,7 +18632,9 @@
         <v>550</v>
       </c>
       <c r="I391" s="4"/>
-      <c r="J391" s="7"/>
+      <c r="J391" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K391" s="8"/>
       <c r="L391" s="8"/>
     </row>
@@ -17775,7 +18660,9 @@
       <c r="G392" s="3"/>
       <c r="H392" s="4"/>
       <c r="I392" s="4"/>
-      <c r="J392" s="7"/>
+      <c r="J392" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K392" s="8"/>
       <c r="L392" s="8"/>
     </row>
@@ -17801,7 +18688,9 @@
       <c r="G393" s="3"/>
       <c r="H393" s="4"/>
       <c r="I393" s="4"/>
-      <c r="J393" s="7"/>
+      <c r="J393" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K393" s="8"/>
       <c r="L393" s="8"/>
     </row>
@@ -17827,7 +18716,9 @@
       <c r="G394" s="3"/>
       <c r="H394" s="4"/>
       <c r="I394" s="4"/>
-      <c r="J394" s="7"/>
+      <c r="J394" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K394" s="8"/>
       <c r="L394" s="8"/>
     </row>
@@ -17853,7 +18744,9 @@
       <c r="G395" s="3"/>
       <c r="H395" s="4"/>
       <c r="I395" s="4"/>
-      <c r="J395" s="7"/>
+      <c r="J395" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K395" s="8"/>
       <c r="L395" s="8"/>
     </row>
@@ -17879,7 +18772,9 @@
       <c r="G396" s="3"/>
       <c r="H396" s="4"/>
       <c r="I396" s="4"/>
-      <c r="J396" s="7"/>
+      <c r="J396" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K396" s="8"/>
       <c r="L396" s="8"/>
     </row>
@@ -17909,7 +18804,9 @@
         <v>1388</v>
       </c>
       <c r="I397" s="4"/>
-      <c r="J397" s="7"/>
+      <c r="J397" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K397" s="8"/>
       <c r="L397" s="8"/>
     </row>
@@ -17933,8 +18830,12 @@
       <c r="G398" s="3"/>
       <c r="H398" s="4"/>
       <c r="I398" s="4"/>
-      <c r="J398" s="7"/>
-      <c r="K398" s="8"/>
+      <c r="J398" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K398" s="8" t="s">
+        <v>2241</v>
+      </c>
       <c r="L398" s="8"/>
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.2">
@@ -17959,8 +18860,12 @@
         <v>266</v>
       </c>
       <c r="I399" s="4"/>
-      <c r="J399" s="7"/>
-      <c r="K399" s="8"/>
+      <c r="J399" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K399" s="8" t="s">
+        <v>2242</v>
+      </c>
       <c r="L399" s="8"/>
     </row>
     <row r="400" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
@@ -17983,7 +18888,9 @@
       <c r="G400" s="3"/>
       <c r="H400" s="4"/>
       <c r="I400" s="4"/>
-      <c r="J400" s="7"/>
+      <c r="J400" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K400" s="8"/>
       <c r="L400" s="8"/>
     </row>
@@ -18007,7 +18914,9 @@
       <c r="G401" s="3"/>
       <c r="H401" s="4"/>
       <c r="I401" s="4"/>
-      <c r="J401" s="7"/>
+      <c r="J401" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K401" s="8"/>
       <c r="L401" s="8"/>
     </row>
@@ -18037,8 +18946,12 @@
         <v>1403</v>
       </c>
       <c r="I402" s="4"/>
-      <c r="J402" s="7"/>
-      <c r="K402" s="8"/>
+      <c r="J402" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K402" s="8" t="s">
+        <v>2243</v>
+      </c>
       <c r="L402" s="8"/>
     </row>
     <row r="403" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
@@ -18067,8 +18980,12 @@
         <v>1408</v>
       </c>
       <c r="I403" s="4"/>
-      <c r="J403" s="7"/>
-      <c r="K403" s="8"/>
+      <c r="J403" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K403" s="8" t="s">
+        <v>2244</v>
+      </c>
       <c r="L403" s="8"/>
     </row>
     <row r="404" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
@@ -18097,7 +19014,9 @@
         <v>1413</v>
       </c>
       <c r="I404" s="4"/>
-      <c r="J404" s="7"/>
+      <c r="J404" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K404" s="8"/>
       <c r="L404" s="8"/>
     </row>
@@ -18121,7 +19040,9 @@
       <c r="G405" s="3"/>
       <c r="H405" s="4"/>
       <c r="I405" s="4"/>
-      <c r="J405" s="7"/>
+      <c r="J405" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K405" s="8"/>
       <c r="L405" s="8"/>
     </row>
@@ -18151,7 +19072,9 @@
         <v>1420</v>
       </c>
       <c r="I406" s="4"/>
-      <c r="J406" s="7"/>
+      <c r="J406" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K406" s="8"/>
       <c r="L406" s="8"/>
     </row>
@@ -18177,7 +19100,9 @@
       <c r="G407" s="3"/>
       <c r="H407" s="4"/>
       <c r="I407" s="4"/>
-      <c r="J407" s="7"/>
+      <c r="J407" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K407" s="8"/>
       <c r="L407" s="8"/>
     </row>
@@ -18205,7 +19130,9 @@
         <v>1429</v>
       </c>
       <c r="I408" s="4"/>
-      <c r="J408" s="7"/>
+      <c r="J408" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K408" s="8"/>
       <c r="L408" s="8"/>
     </row>
@@ -18231,7 +19158,9 @@
       <c r="G409" s="3"/>
       <c r="H409" s="4"/>
       <c r="I409" s="4"/>
-      <c r="J409" s="7"/>
+      <c r="J409" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K409" s="8"/>
       <c r="L409" s="8"/>
     </row>
@@ -18261,7 +19190,9 @@
         <v>1437</v>
       </c>
       <c r="I410" s="4"/>
-      <c r="J410" s="7"/>
+      <c r="J410" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K410" s="8"/>
       <c r="L410" s="8"/>
     </row>
@@ -18287,7 +19218,9 @@
         <v>24</v>
       </c>
       <c r="I411" s="4"/>
-      <c r="J411" s="7"/>
+      <c r="J411" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K411" s="8"/>
       <c r="L411" s="8"/>
     </row>
@@ -18311,7 +19244,9 @@
       <c r="G412" s="3"/>
       <c r="H412" s="4"/>
       <c r="I412" s="4"/>
-      <c r="J412" s="7"/>
+      <c r="J412" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K412" s="8"/>
       <c r="L412" s="8"/>
     </row>
@@ -18335,7 +19270,9 @@
       <c r="G413" s="3"/>
       <c r="H413" s="4"/>
       <c r="I413" s="4"/>
-      <c r="J413" s="7"/>
+      <c r="J413" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K413" s="8"/>
       <c r="L413" s="8"/>
     </row>
@@ -18359,7 +19296,9 @@
       <c r="G414" s="3"/>
       <c r="H414" s="4"/>
       <c r="I414" s="4"/>
-      <c r="J414" s="7"/>
+      <c r="J414" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K414" s="8"/>
       <c r="L414" s="8"/>
     </row>
@@ -18383,7 +19322,9 @@
       <c r="G415" s="3"/>
       <c r="H415" s="4"/>
       <c r="I415" s="4"/>
-      <c r="J415" s="7"/>
+      <c r="J415" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K415" s="8"/>
       <c r="L415" s="8"/>
     </row>
@@ -18407,7 +19348,9 @@
       <c r="G416" s="3"/>
       <c r="H416" s="4"/>
       <c r="I416" s="4"/>
-      <c r="J416" s="7"/>
+      <c r="J416" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K416" s="8"/>
       <c r="L416" s="8"/>
     </row>
@@ -18431,8 +19374,12 @@
       <c r="G417" s="3"/>
       <c r="H417" s="4"/>
       <c r="I417" s="4"/>
-      <c r="J417" s="7"/>
-      <c r="K417" s="8"/>
+      <c r="J417" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K417" s="8" t="s">
+        <v>2243</v>
+      </c>
       <c r="L417" s="8"/>
     </row>
     <row r="418" spans="1:12" x14ac:dyDescent="0.2">
@@ -18461,7 +19408,9 @@
         <v>1460</v>
       </c>
       <c r="I418" s="4"/>
-      <c r="J418" s="7"/>
+      <c r="J418" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K418" s="8"/>
       <c r="L418" s="8"/>
     </row>
@@ -18491,7 +19440,9 @@
         <v>1465</v>
       </c>
       <c r="I419" s="4"/>
-      <c r="J419" s="7"/>
+      <c r="J419" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K419" s="8"/>
       <c r="L419" s="8"/>
     </row>
@@ -18517,8 +19468,12 @@
       <c r="G420" s="3"/>
       <c r="H420" s="4"/>
       <c r="I420" s="4"/>
-      <c r="J420" s="7"/>
-      <c r="K420" s="8"/>
+      <c r="J420" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K420" s="8" t="s">
+        <v>2245</v>
+      </c>
       <c r="L420" s="8"/>
     </row>
     <row r="421" spans="1:12" x14ac:dyDescent="0.2">
@@ -18547,7 +19502,9 @@
         <v>1465</v>
       </c>
       <c r="I421" s="4"/>
-      <c r="J421" s="7"/>
+      <c r="J421" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K421" s="8"/>
       <c r="L421" s="8"/>
     </row>
@@ -18579,7 +19536,9 @@
       <c r="I422" s="10" t="s">
         <v>1478</v>
       </c>
-      <c r="J422" s="7"/>
+      <c r="J422" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K422" s="8"/>
       <c r="L422" s="8"/>
     </row>
@@ -18609,7 +19568,9 @@
         <v>1465</v>
       </c>
       <c r="I423" s="4"/>
-      <c r="J423" s="7"/>
+      <c r="J423" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K423" s="8"/>
       <c r="L423" s="8"/>
     </row>
@@ -18639,7 +19600,9 @@
         <v>1465</v>
       </c>
       <c r="I424" s="4"/>
-      <c r="J424" s="7"/>
+      <c r="J424" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K424" s="8"/>
       <c r="L424" s="8"/>
     </row>
@@ -18669,7 +19632,9 @@
         <v>1465</v>
       </c>
       <c r="I425" s="4"/>
-      <c r="J425" s="7"/>
+      <c r="J425" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K425" s="8"/>
       <c r="L425" s="8"/>
     </row>
@@ -18699,7 +19664,9 @@
         <v>1495</v>
       </c>
       <c r="I426" s="4"/>
-      <c r="J426" s="7"/>
+      <c r="J426" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K426" s="8"/>
       <c r="L426" s="8"/>
     </row>
@@ -18725,8 +19692,12 @@
       <c r="G427" s="3"/>
       <c r="H427" s="4"/>
       <c r="I427" s="4"/>
-      <c r="J427" s="7"/>
-      <c r="K427" s="8"/>
+      <c r="J427" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K427" s="8" t="s">
+        <v>2246</v>
+      </c>
       <c r="L427" s="8"/>
     </row>
     <row r="428" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
@@ -18751,7 +19722,9 @@
       <c r="G428" s="3"/>
       <c r="H428" s="4"/>
       <c r="I428" s="4"/>
-      <c r="J428" s="7"/>
+      <c r="J428" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K428" s="8"/>
       <c r="L428" s="8"/>
     </row>
@@ -18777,7 +19750,9 @@
       <c r="G429" s="3"/>
       <c r="H429" s="4"/>
       <c r="I429" s="4"/>
-      <c r="J429" s="7"/>
+      <c r="J429" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K429" s="8"/>
       <c r="L429" s="8"/>
     </row>
@@ -18803,7 +19778,9 @@
       <c r="G430" s="3"/>
       <c r="H430" s="4"/>
       <c r="I430" s="4"/>
-      <c r="J430" s="7"/>
+      <c r="J430" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K430" s="8"/>
       <c r="L430" s="8"/>
     </row>
@@ -18827,7 +19804,9 @@
       <c r="G431" s="3"/>
       <c r="H431" s="4"/>
       <c r="I431" s="4"/>
-      <c r="J431" s="7"/>
+      <c r="J431" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K431" s="8"/>
       <c r="L431" s="8"/>
     </row>
@@ -18851,7 +19830,9 @@
       <c r="G432" s="3"/>
       <c r="H432" s="4"/>
       <c r="I432" s="4"/>
-      <c r="J432" s="7"/>
+      <c r="J432" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K432" s="8"/>
       <c r="L432" s="8"/>
     </row>
@@ -18875,7 +19856,9 @@
       <c r="G433" s="3"/>
       <c r="H433" s="4"/>
       <c r="I433" s="4"/>
-      <c r="J433" s="7"/>
+      <c r="J433" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K433" s="8"/>
       <c r="L433" s="8"/>
     </row>
@@ -18905,7 +19888,9 @@
         <v>1521</v>
       </c>
       <c r="I434" s="4"/>
-      <c r="J434" s="7"/>
+      <c r="J434" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K434" s="8"/>
       <c r="L434" s="8"/>
     </row>
@@ -18929,7 +19914,9 @@
       <c r="G435" s="3"/>
       <c r="H435" s="4"/>
       <c r="I435" s="4"/>
-      <c r="J435" s="7"/>
+      <c r="J435" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K435" s="8"/>
       <c r="L435" s="8"/>
     </row>
@@ -18955,7 +19942,9 @@
       <c r="G436" s="3"/>
       <c r="H436" s="4"/>
       <c r="I436" s="4"/>
-      <c r="J436" s="7"/>
+      <c r="J436" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K436" s="8"/>
       <c r="L436" s="8"/>
     </row>
@@ -18981,7 +19970,9 @@
       <c r="G437" s="3"/>
       <c r="H437" s="4"/>
       <c r="I437" s="4"/>
-      <c r="J437" s="7"/>
+      <c r="J437" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K437" s="8"/>
       <c r="L437" s="8"/>
     </row>
@@ -19007,7 +19998,9 @@
       <c r="G438" s="3"/>
       <c r="H438" s="4"/>
       <c r="I438" s="4"/>
-      <c r="J438" s="7"/>
+      <c r="J438" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K438" s="8"/>
       <c r="L438" s="8"/>
     </row>
@@ -19033,7 +20026,9 @@
       <c r="G439" s="3"/>
       <c r="H439" s="4"/>
       <c r="I439" s="4"/>
-      <c r="J439" s="7"/>
+      <c r="J439" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K439" s="8"/>
       <c r="L439" s="8"/>
     </row>
@@ -19059,7 +20054,9 @@
       <c r="G440" s="3"/>
       <c r="H440" s="4"/>
       <c r="I440" s="4"/>
-      <c r="J440" s="7"/>
+      <c r="J440" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K440" s="8"/>
       <c r="L440" s="8"/>
     </row>
@@ -19083,7 +20080,9 @@
       <c r="G441" s="3"/>
       <c r="H441" s="4"/>
       <c r="I441" s="4"/>
-      <c r="J441" s="7"/>
+      <c r="J441" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K441" s="8"/>
       <c r="L441" s="8"/>
     </row>
@@ -19111,7 +20110,9 @@
         <v>1548</v>
       </c>
       <c r="I442" s="4"/>
-      <c r="J442" s="7"/>
+      <c r="J442" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K442" s="8"/>
       <c r="L442" s="8"/>
     </row>
@@ -19141,7 +20142,9 @@
         <v>1553</v>
       </c>
       <c r="I443" s="4"/>
-      <c r="J443" s="7"/>
+      <c r="J443" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K443" s="8"/>
       <c r="L443" s="8"/>
     </row>
@@ -19171,7 +20174,9 @@
         <v>1558</v>
       </c>
       <c r="I444" s="4"/>
-      <c r="J444" s="7"/>
+      <c r="J444" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K444" s="8"/>
       <c r="L444" s="8"/>
     </row>
@@ -19197,7 +20202,9 @@
       <c r="G445" s="3"/>
       <c r="H445" s="4"/>
       <c r="I445" s="4"/>
-      <c r="J445" s="7"/>
+      <c r="J445" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K445" s="8"/>
       <c r="L445" s="8"/>
     </row>
@@ -19223,7 +20230,9 @@
       <c r="G446" s="3"/>
       <c r="H446" s="4"/>
       <c r="I446" s="4"/>
-      <c r="J446" s="7"/>
+      <c r="J446" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K446" s="8"/>
       <c r="L446" s="8"/>
     </row>
@@ -19249,7 +20258,9 @@
       <c r="G447" s="3"/>
       <c r="H447" s="4"/>
       <c r="I447" s="4"/>
-      <c r="J447" s="7"/>
+      <c r="J447" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K447" s="8"/>
       <c r="L447" s="8"/>
     </row>
@@ -19279,7 +20290,9 @@
         <v>1570</v>
       </c>
       <c r="I448" s="4"/>
-      <c r="J448" s="7"/>
+      <c r="J448" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K448" s="8"/>
       <c r="L448" s="8"/>
     </row>
@@ -19309,7 +20322,9 @@
         <v>1575</v>
       </c>
       <c r="I449" s="4"/>
-      <c r="J449" s="7"/>
+      <c r="J449" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K449" s="8"/>
       <c r="L449" s="8"/>
     </row>
@@ -19339,7 +20354,9 @@
         <v>1580</v>
       </c>
       <c r="I450" s="4"/>
-      <c r="J450" s="7"/>
+      <c r="J450" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K450" s="8"/>
       <c r="L450" s="8"/>
     </row>
@@ -19369,7 +20386,9 @@
         <v>1585</v>
       </c>
       <c r="I451" s="4"/>
-      <c r="J451" s="7"/>
+      <c r="J451" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K451" s="8"/>
       <c r="L451" s="8"/>
     </row>
@@ -19395,7 +20414,9 @@
       <c r="G452" s="3"/>
       <c r="H452" s="4"/>
       <c r="I452" s="4"/>
-      <c r="J452" s="7"/>
+      <c r="J452" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K452" s="8"/>
       <c r="L452" s="8"/>
     </row>
@@ -19419,7 +20440,9 @@
       <c r="G453" s="3"/>
       <c r="H453" s="4"/>
       <c r="I453" s="4"/>
-      <c r="J453" s="7"/>
+      <c r="J453" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K453" s="8"/>
       <c r="L453" s="8"/>
     </row>
@@ -19447,7 +20470,9 @@
         <v>367</v>
       </c>
       <c r="I454" s="4"/>
-      <c r="J454" s="7"/>
+      <c r="J454" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K454" s="8"/>
       <c r="L454" s="8"/>
     </row>
@@ -19471,7 +20496,9 @@
       <c r="G455" s="3"/>
       <c r="H455" s="4"/>
       <c r="I455" s="4"/>
-      <c r="J455" s="7"/>
+      <c r="J455" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K455" s="8"/>
       <c r="L455" s="8"/>
     </row>
@@ -19499,7 +20526,9 @@
         <v>367</v>
       </c>
       <c r="I456" s="4"/>
-      <c r="J456" s="7"/>
+      <c r="J456" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K456" s="8"/>
       <c r="L456" s="8"/>
     </row>
@@ -19525,7 +20554,9 @@
       <c r="G457" s="3"/>
       <c r="H457" s="4"/>
       <c r="I457" s="4"/>
-      <c r="J457" s="7"/>
+      <c r="J457" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K457" s="8"/>
       <c r="L457" s="8"/>
     </row>
@@ -19551,8 +20582,12 @@
         <v>1602</v>
       </c>
       <c r="I458" s="4"/>
-      <c r="J458" s="7"/>
-      <c r="K458" s="8"/>
+      <c r="J458" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K458" s="8" t="s">
+        <v>2247</v>
+      </c>
       <c r="L458" s="8"/>
     </row>
     <row r="459" spans="1:12" x14ac:dyDescent="0.2">
@@ -19575,7 +20610,9 @@
       <c r="G459" s="3"/>
       <c r="H459" s="4"/>
       <c r="I459" s="4"/>
-      <c r="J459" s="7"/>
+      <c r="J459" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K459" s="8"/>
       <c r="L459" s="8"/>
     </row>
@@ -19599,7 +20636,9 @@
       <c r="G460" s="3"/>
       <c r="H460" s="4"/>
       <c r="I460" s="4"/>
-      <c r="J460" s="7"/>
+      <c r="J460" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K460" s="8"/>
       <c r="L460" s="8"/>
     </row>
@@ -19625,7 +20664,9 @@
       <c r="G461" s="3"/>
       <c r="H461" s="4"/>
       <c r="I461" s="4"/>
-      <c r="J461" s="7"/>
+      <c r="J461" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K461" s="8"/>
       <c r="L461" s="8"/>
     </row>
@@ -19649,7 +20690,9 @@
       <c r="G462" s="3"/>
       <c r="H462" s="4"/>
       <c r="I462" s="4"/>
-      <c r="J462" s="7"/>
+      <c r="J462" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K462" s="8"/>
       <c r="L462" s="8"/>
     </row>
@@ -19673,7 +20716,9 @@
       <c r="G463" s="3"/>
       <c r="H463" s="4"/>
       <c r="I463" s="4"/>
-      <c r="J463" s="7"/>
+      <c r="J463" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K463" s="8"/>
       <c r="L463" s="8"/>
     </row>
@@ -19705,7 +20750,9 @@
       <c r="I464" s="10" t="s">
         <v>1621</v>
       </c>
-      <c r="J464" s="7"/>
+      <c r="J464" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K464" s="8"/>
       <c r="L464" s="8"/>
     </row>
@@ -19733,7 +20780,9 @@
       <c r="I465" s="10" t="s">
         <v>1625</v>
       </c>
-      <c r="J465" s="7"/>
+      <c r="J465" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K465" s="8"/>
       <c r="L465" s="8"/>
     </row>
@@ -19761,7 +20810,9 @@
       <c r="I466" s="10" t="s">
         <v>1629</v>
       </c>
-      <c r="J466" s="7"/>
+      <c r="J466" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K466" s="8"/>
       <c r="L466" s="8"/>
     </row>
@@ -19785,7 +20836,9 @@
       <c r="G467" s="3"/>
       <c r="H467" s="4"/>
       <c r="I467" s="4"/>
-      <c r="J467" s="7"/>
+      <c r="J467" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K467" s="8"/>
       <c r="L467" s="8"/>
     </row>
@@ -19811,7 +20864,9 @@
       <c r="G468" s="3"/>
       <c r="H468" s="4"/>
       <c r="I468" s="4"/>
-      <c r="J468" s="7"/>
+      <c r="J468" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K468" s="8"/>
       <c r="L468" s="8"/>
     </row>
@@ -19841,7 +20896,9 @@
         <v>1640</v>
       </c>
       <c r="I469" s="4"/>
-      <c r="J469" s="7"/>
+      <c r="J469" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K469" s="8"/>
       <c r="L469" s="8"/>
     </row>
@@ -19867,7 +20924,9 @@
       <c r="G470" s="3"/>
       <c r="H470" s="4"/>
       <c r="I470" s="4"/>
-      <c r="J470" s="7"/>
+      <c r="J470" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K470" s="8"/>
       <c r="L470" s="8"/>
     </row>
@@ -19893,7 +20952,9 @@
       <c r="G471" s="3"/>
       <c r="H471" s="4"/>
       <c r="I471" s="4"/>
-      <c r="J471" s="7"/>
+      <c r="J471" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K471" s="8"/>
       <c r="L471" s="8"/>
     </row>
@@ -19919,7 +20980,9 @@
       <c r="G472" s="3"/>
       <c r="H472" s="4"/>
       <c r="I472" s="4"/>
-      <c r="J472" s="7"/>
+      <c r="J472" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K472" s="8"/>
       <c r="L472" s="8"/>
     </row>
@@ -19945,7 +21008,9 @@
       <c r="G473" s="3"/>
       <c r="H473" s="4"/>
       <c r="I473" s="4"/>
-      <c r="J473" s="7"/>
+      <c r="J473" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K473" s="8"/>
       <c r="L473" s="8"/>
     </row>
@@ -19975,7 +21040,9 @@
         <v>1659</v>
       </c>
       <c r="I474" s="4"/>
-      <c r="J474" s="7"/>
+      <c r="J474" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K474" s="8"/>
       <c r="L474" s="8"/>
     </row>
@@ -20001,7 +21068,9 @@
       <c r="G475" s="3"/>
       <c r="H475" s="4"/>
       <c r="I475" s="4"/>
-      <c r="J475" s="7"/>
+      <c r="J475" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K475" s="8"/>
       <c r="L475" s="8"/>
     </row>
@@ -20029,7 +21098,9 @@
         <v>1666</v>
       </c>
       <c r="I476" s="4"/>
-      <c r="J476" s="7"/>
+      <c r="J476" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K476" s="8"/>
       <c r="L476" s="8"/>
     </row>
@@ -20055,7 +21126,9 @@
       <c r="G477" s="3"/>
       <c r="H477" s="4"/>
       <c r="I477" s="4"/>
-      <c r="J477" s="7"/>
+      <c r="J477" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K477" s="8"/>
       <c r="L477" s="8"/>
     </row>
@@ -20079,7 +21152,9 @@
       <c r="G478" s="3"/>
       <c r="H478" s="4"/>
       <c r="I478" s="4"/>
-      <c r="J478" s="7"/>
+      <c r="J478" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K478" s="8"/>
       <c r="L478" s="8"/>
     </row>
@@ -20105,7 +21180,9 @@
       <c r="G479" s="3"/>
       <c r="H479" s="4"/>
       <c r="I479" s="4"/>
-      <c r="J479" s="7"/>
+      <c r="J479" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K479" s="8"/>
       <c r="L479" s="8"/>
     </row>
@@ -20131,7 +21208,9 @@
       <c r="G480" s="3"/>
       <c r="H480" s="4"/>
       <c r="I480" s="4"/>
-      <c r="J480" s="7"/>
+      <c r="J480" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K480" s="8"/>
       <c r="L480" s="8"/>
     </row>
@@ -20155,7 +21234,9 @@
       <c r="G481" s="3"/>
       <c r="H481" s="4"/>
       <c r="I481" s="4"/>
-      <c r="J481" s="7"/>
+      <c r="J481" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K481" s="8"/>
       <c r="L481" s="8"/>
     </row>
@@ -20181,7 +21262,9 @@
       <c r="G482" s="3"/>
       <c r="H482" s="4"/>
       <c r="I482" s="4"/>
-      <c r="J482" s="7"/>
+      <c r="J482" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K482" s="8"/>
       <c r="L482" s="8"/>
     </row>
@@ -20207,7 +21290,9 @@
       <c r="G483" s="3"/>
       <c r="H483" s="4"/>
       <c r="I483" s="4"/>
-      <c r="J483" s="7"/>
+      <c r="J483" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K483" s="8"/>
       <c r="L483" s="8"/>
     </row>
@@ -20233,7 +21318,9 @@
       <c r="G484" s="3"/>
       <c r="H484" s="4"/>
       <c r="I484" s="4"/>
-      <c r="J484" s="7"/>
+      <c r="J484" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K484" s="8"/>
       <c r="L484" s="8"/>
     </row>
@@ -20259,7 +21346,9 @@
       <c r="G485" s="3"/>
       <c r="H485" s="4"/>
       <c r="I485" s="4"/>
-      <c r="J485" s="7"/>
+      <c r="J485" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K485" s="8"/>
       <c r="L485" s="8"/>
     </row>
@@ -20285,7 +21374,9 @@
       <c r="G486" s="3"/>
       <c r="H486" s="4"/>
       <c r="I486" s="4"/>
-      <c r="J486" s="7"/>
+      <c r="J486" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K486" s="8"/>
       <c r="L486" s="8"/>
     </row>
@@ -20311,7 +21402,9 @@
       <c r="G487" s="3"/>
       <c r="H487" s="4"/>
       <c r="I487" s="4"/>
-      <c r="J487" s="7"/>
+      <c r="J487" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K487" s="8"/>
       <c r="L487" s="8"/>
     </row>
@@ -20337,7 +21430,9 @@
       <c r="G488" s="3"/>
       <c r="H488" s="4"/>
       <c r="I488" s="4"/>
-      <c r="J488" s="7"/>
+      <c r="J488" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K488" s="8"/>
       <c r="L488" s="8"/>
     </row>
@@ -20367,7 +21462,9 @@
         <v>1711</v>
       </c>
       <c r="I489" s="4"/>
-      <c r="J489" s="7"/>
+      <c r="J489" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K489" s="8"/>
       <c r="L489" s="8"/>
     </row>
@@ -20393,7 +21490,9 @@
       <c r="G490" s="3"/>
       <c r="H490" s="4"/>
       <c r="I490" s="4"/>
-      <c r="J490" s="7"/>
+      <c r="J490" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K490" s="8"/>
       <c r="L490" s="8"/>
     </row>
@@ -20421,7 +21520,9 @@
         <v>789</v>
       </c>
       <c r="I491" s="4"/>
-      <c r="J491" s="7"/>
+      <c r="J491" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K491" s="8"/>
       <c r="L491" s="8"/>
     </row>
@@ -20447,7 +21548,9 @@
       <c r="G492" s="3"/>
       <c r="H492" s="4"/>
       <c r="I492" s="4"/>
-      <c r="J492" s="7"/>
+      <c r="J492" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K492" s="8"/>
       <c r="L492" s="8"/>
     </row>
@@ -20473,7 +21576,9 @@
       <c r="G493" s="3"/>
       <c r="H493" s="4"/>
       <c r="I493" s="4"/>
-      <c r="J493" s="7"/>
+      <c r="J493" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K493" s="8"/>
       <c r="L493" s="8"/>
     </row>
@@ -20497,7 +21602,9 @@
       <c r="G494" s="3"/>
       <c r="H494" s="4"/>
       <c r="I494" s="4"/>
-      <c r="J494" s="7"/>
+      <c r="J494" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K494" s="8"/>
       <c r="L494" s="8"/>
     </row>
@@ -20527,8 +21634,12 @@
         <v>1732</v>
       </c>
       <c r="I495" s="4"/>
-      <c r="J495" s="7"/>
-      <c r="K495" s="8"/>
+      <c r="J495" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K495" s="8" t="s">
+        <v>2248</v>
+      </c>
       <c r="L495" s="8"/>
     </row>
     <row r="496" spans="1:12" x14ac:dyDescent="0.2">
@@ -20553,7 +21664,9 @@
       <c r="G496" s="3"/>
       <c r="H496" s="4"/>
       <c r="I496" s="4"/>
-      <c r="J496" s="7"/>
+      <c r="J496" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K496" s="8"/>
       <c r="L496" s="8"/>
     </row>
@@ -20583,7 +21696,9 @@
         <v>1739</v>
       </c>
       <c r="I497" s="4"/>
-      <c r="J497" s="7"/>
+      <c r="J497" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K497" s="8"/>
       <c r="L497" s="8"/>
     </row>
@@ -20609,7 +21724,9 @@
       <c r="G498" s="3"/>
       <c r="H498" s="4"/>
       <c r="I498" s="4"/>
-      <c r="J498" s="7"/>
+      <c r="J498" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K498" s="8"/>
       <c r="L498" s="8"/>
     </row>
@@ -20639,7 +21756,9 @@
         <v>1748</v>
       </c>
       <c r="I499" s="4"/>
-      <c r="J499" s="7"/>
+      <c r="J499" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K499" s="8"/>
       <c r="L499" s="8"/>
     </row>
@@ -20665,7 +21784,9 @@
       <c r="G500" s="3"/>
       <c r="H500" s="4"/>
       <c r="I500" s="4"/>
-      <c r="J500" s="7"/>
+      <c r="J500" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K500" s="8"/>
       <c r="L500" s="8"/>
     </row>
@@ -20691,7 +21812,9 @@
         <v>24</v>
       </c>
       <c r="I501" s="4"/>
-      <c r="J501" s="7"/>
+      <c r="J501" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K501" s="8"/>
       <c r="L501" s="8"/>
     </row>
@@ -20721,7 +21844,9 @@
         <v>1035</v>
       </c>
       <c r="I502" s="4"/>
-      <c r="J502" s="7"/>
+      <c r="J502" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K502" s="8"/>
       <c r="L502" s="8"/>
     </row>
@@ -20747,7 +21872,9 @@
         <v>24</v>
       </c>
       <c r="I503" s="4"/>
-      <c r="J503" s="7"/>
+      <c r="J503" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K503" s="8"/>
       <c r="L503" s="8"/>
     </row>
@@ -20773,7 +21900,9 @@
         <v>1766</v>
       </c>
       <c r="I504" s="4"/>
-      <c r="J504" s="7"/>
+      <c r="J504" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K504" s="8"/>
       <c r="L504" s="8"/>
     </row>
@@ -20799,7 +21928,9 @@
         <v>24</v>
       </c>
       <c r="I505" s="4"/>
-      <c r="J505" s="7"/>
+      <c r="J505" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K505" s="8"/>
       <c r="L505" s="8"/>
     </row>
@@ -20823,7 +21954,9 @@
       <c r="G506" s="3"/>
       <c r="H506" s="4"/>
       <c r="I506" s="4"/>
-      <c r="J506" s="7"/>
+      <c r="J506" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K506" s="8"/>
       <c r="L506" s="8"/>
     </row>
@@ -20853,7 +21986,9 @@
       <c r="I507" s="10" t="s">
         <v>1777</v>
       </c>
-      <c r="J507" s="7"/>
+      <c r="J507" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K507" s="8"/>
       <c r="L507" s="8"/>
     </row>
@@ -20879,7 +22014,9 @@
       <c r="G508" s="3"/>
       <c r="H508" s="4"/>
       <c r="I508" s="4"/>
-      <c r="J508" s="7"/>
+      <c r="J508" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K508" s="8"/>
       <c r="L508" s="8"/>
     </row>
@@ -20903,7 +22040,9 @@
       <c r="G509" s="3"/>
       <c r="H509" s="4"/>
       <c r="I509" s="4"/>
-      <c r="J509" s="7"/>
+      <c r="J509" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K509" s="8"/>
       <c r="L509" s="8"/>
     </row>
@@ -20929,7 +22068,9 @@
       <c r="G510" s="3"/>
       <c r="H510" s="4"/>
       <c r="I510" s="4"/>
-      <c r="J510" s="7"/>
+      <c r="J510" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K510" s="8"/>
       <c r="L510" s="8"/>
     </row>
@@ -20955,7 +22096,9 @@
       <c r="G511" s="3"/>
       <c r="H511" s="4"/>
       <c r="I511" s="4"/>
-      <c r="J511" s="7"/>
+      <c r="J511" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K511" s="8"/>
       <c r="L511" s="8"/>
     </row>
@@ -20981,7 +22124,9 @@
         <v>266</v>
       </c>
       <c r="I512" s="4"/>
-      <c r="J512" s="7"/>
+      <c r="J512" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K512" s="8"/>
       <c r="L512" s="8"/>
     </row>
@@ -21007,7 +22152,9 @@
         <v>24</v>
       </c>
       <c r="I513" s="4"/>
-      <c r="J513" s="7"/>
+      <c r="J513" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K513" s="8"/>
       <c r="L513" s="8"/>
     </row>
@@ -21037,7 +22184,9 @@
         <v>1800</v>
       </c>
       <c r="I514" s="4"/>
-      <c r="J514" s="7"/>
+      <c r="J514" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K514" s="8"/>
       <c r="L514" s="8"/>
     </row>
@@ -21063,7 +22212,9 @@
       <c r="G515" s="3"/>
       <c r="H515" s="4"/>
       <c r="I515" s="4"/>
-      <c r="J515" s="7"/>
+      <c r="J515" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K515" s="8"/>
       <c r="L515" s="8"/>
     </row>
@@ -21089,7 +22240,9 @@
       <c r="G516" s="3"/>
       <c r="H516" s="4"/>
       <c r="I516" s="4"/>
-      <c r="J516" s="7"/>
+      <c r="J516" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K516" s="8"/>
       <c r="L516" s="8"/>
     </row>
@@ -21117,7 +22270,9 @@
         <v>1810</v>
       </c>
       <c r="I517" s="4"/>
-      <c r="J517" s="7"/>
+      <c r="J517" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K517" s="8"/>
       <c r="L517" s="8"/>
     </row>
@@ -21143,7 +22298,9 @@
       <c r="G518" s="3"/>
       <c r="H518" s="4"/>
       <c r="I518" s="4"/>
-      <c r="J518" s="7"/>
+      <c r="J518" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K518" s="8"/>
       <c r="L518" s="8"/>
     </row>
@@ -21169,7 +22326,9 @@
         <v>1818</v>
       </c>
       <c r="I519" s="4"/>
-      <c r="J519" s="7"/>
+      <c r="J519" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K519" s="8"/>
       <c r="L519" s="8"/>
     </row>
@@ -21199,7 +22358,9 @@
         <v>1823</v>
       </c>
       <c r="I520" s="4"/>
-      <c r="J520" s="7"/>
+      <c r="J520" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K520" s="8"/>
       <c r="L520" s="8"/>
     </row>
@@ -21223,7 +22384,9 @@
       <c r="G521" s="3"/>
       <c r="H521" s="4"/>
       <c r="I521" s="4"/>
-      <c r="J521" s="7"/>
+      <c r="J521" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K521" s="8"/>
       <c r="L521" s="8"/>
     </row>
@@ -21249,7 +22412,9 @@
       <c r="G522" s="3"/>
       <c r="H522" s="4"/>
       <c r="I522" s="4"/>
-      <c r="J522" s="7"/>
+      <c r="J522" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K522" s="8"/>
       <c r="L522" s="8"/>
     </row>
@@ -21273,7 +22438,9 @@
       <c r="G523" s="3"/>
       <c r="H523" s="4"/>
       <c r="I523" s="4"/>
-      <c r="J523" s="7"/>
+      <c r="J523" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K523" s="8"/>
       <c r="L523" s="8"/>
     </row>
@@ -21299,7 +22466,9 @@
       <c r="G524" s="3"/>
       <c r="H524" s="4"/>
       <c r="I524" s="4"/>
-      <c r="J524" s="7"/>
+      <c r="J524" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K524" s="8"/>
       <c r="L524" s="8"/>
     </row>
@@ -21329,7 +22498,9 @@
         <v>1840</v>
       </c>
       <c r="I525" s="4"/>
-      <c r="J525" s="7"/>
+      <c r="J525" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K525" s="8"/>
       <c r="L525" s="8"/>
     </row>
@@ -21359,7 +22530,9 @@
         <v>1845</v>
       </c>
       <c r="I526" s="4"/>
-      <c r="J526" s="7"/>
+      <c r="J526" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K526" s="8"/>
       <c r="L526" s="8"/>
     </row>
@@ -21385,7 +22558,9 @@
       <c r="G527" s="3"/>
       <c r="H527" s="4"/>
       <c r="I527" s="4"/>
-      <c r="J527" s="7"/>
+      <c r="J527" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K527" s="8"/>
       <c r="L527" s="8"/>
     </row>
@@ -21411,7 +22586,9 @@
       <c r="G528" s="3"/>
       <c r="H528" s="4"/>
       <c r="I528" s="4"/>
-      <c r="J528" s="7"/>
+      <c r="J528" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K528" s="8"/>
       <c r="L528" s="8"/>
     </row>
@@ -21437,7 +22614,9 @@
       <c r="G529" s="3"/>
       <c r="H529" s="4"/>
       <c r="I529" s="4"/>
-      <c r="J529" s="7"/>
+      <c r="J529" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K529" s="8"/>
       <c r="L529" s="8"/>
     </row>
@@ -21463,7 +22642,9 @@
       <c r="G530" s="3"/>
       <c r="H530" s="4"/>
       <c r="I530" s="4"/>
-      <c r="J530" s="7"/>
+      <c r="J530" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K530" s="8"/>
       <c r="L530" s="8"/>
     </row>
@@ -21487,7 +22668,9 @@
       <c r="G531" s="3"/>
       <c r="H531" s="4"/>
       <c r="I531" s="4"/>
-      <c r="J531" s="7"/>
+      <c r="J531" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K531" s="8"/>
       <c r="L531" s="8"/>
     </row>
@@ -21511,7 +22694,9 @@
       <c r="G532" s="3"/>
       <c r="H532" s="4"/>
       <c r="I532" s="4"/>
-      <c r="J532" s="7"/>
+      <c r="J532" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K532" s="8"/>
       <c r="L532" s="8"/>
     </row>
@@ -21535,7 +22720,9 @@
       <c r="G533" s="3"/>
       <c r="H533" s="4"/>
       <c r="I533" s="4"/>
-      <c r="J533" s="7"/>
+      <c r="J533" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K533" s="8"/>
       <c r="L533" s="8"/>
     </row>
@@ -21559,7 +22746,9 @@
       <c r="G534" s="3"/>
       <c r="H534" s="4"/>
       <c r="I534" s="4"/>
-      <c r="J534" s="7"/>
+      <c r="J534" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K534" s="8"/>
       <c r="L534" s="8"/>
     </row>
@@ -21583,7 +22772,9 @@
       <c r="G535" s="3"/>
       <c r="H535" s="4"/>
       <c r="I535" s="4"/>
-      <c r="J535" s="7"/>
+      <c r="J535" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K535" s="8"/>
       <c r="L535" s="8"/>
     </row>
@@ -21607,7 +22798,9 @@
       <c r="G536" s="3"/>
       <c r="H536" s="4"/>
       <c r="I536" s="4"/>
-      <c r="J536" s="7"/>
+      <c r="J536" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K536" s="8"/>
       <c r="L536" s="8"/>
     </row>
@@ -21631,7 +22824,9 @@
       <c r="G537" s="3"/>
       <c r="H537" s="4"/>
       <c r="I537" s="4"/>
-      <c r="J537" s="7"/>
+      <c r="J537" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K537" s="8"/>
       <c r="L537" s="8"/>
     </row>
@@ -21655,7 +22850,9 @@
       <c r="G538" s="3"/>
       <c r="H538" s="4"/>
       <c r="I538" s="4"/>
-      <c r="J538" s="7"/>
+      <c r="J538" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K538" s="8"/>
       <c r="L538" s="8"/>
     </row>
@@ -21679,7 +22876,9 @@
       <c r="G539" s="3"/>
       <c r="H539" s="4"/>
       <c r="I539" s="4"/>
-      <c r="J539" s="7"/>
+      <c r="J539" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K539" s="8"/>
       <c r="L539" s="8"/>
     </row>
@@ -21709,7 +22908,9 @@
         <v>1845</v>
       </c>
       <c r="I540" s="4"/>
-      <c r="J540" s="7"/>
+      <c r="J540" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K540" s="8"/>
       <c r="L540" s="8"/>
     </row>
@@ -21735,7 +22936,9 @@
       <c r="G541" s="3"/>
       <c r="H541" s="4"/>
       <c r="I541" s="4"/>
-      <c r="J541" s="7"/>
+      <c r="J541" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K541" s="8"/>
       <c r="L541" s="8"/>
     </row>
@@ -21761,7 +22964,9 @@
       <c r="G542" s="3"/>
       <c r="H542" s="4"/>
       <c r="I542" s="4"/>
-      <c r="J542" s="7"/>
+      <c r="J542" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K542" s="8"/>
       <c r="L542" s="8"/>
     </row>
@@ -21787,7 +22992,9 @@
       <c r="G543" s="3"/>
       <c r="H543" s="4"/>
       <c r="I543" s="4"/>
-      <c r="J543" s="7"/>
+      <c r="J543" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K543" s="8"/>
       <c r="L543" s="8"/>
     </row>
@@ -21813,7 +23020,9 @@
       <c r="G544" s="3"/>
       <c r="H544" s="4"/>
       <c r="I544" s="4"/>
-      <c r="J544" s="7"/>
+      <c r="J544" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K544" s="8"/>
       <c r="L544" s="8"/>
     </row>
@@ -21837,7 +23046,9 @@
       <c r="G545" s="3"/>
       <c r="H545" s="4"/>
       <c r="I545" s="4"/>
-      <c r="J545" s="7"/>
+      <c r="J545" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K545" s="8"/>
       <c r="L545" s="8"/>
     </row>
@@ -21863,7 +23074,9 @@
       <c r="G546" s="3"/>
       <c r="H546" s="4"/>
       <c r="I546" s="4"/>
-      <c r="J546" s="7"/>
+      <c r="J546" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K546" s="8"/>
       <c r="L546" s="8"/>
     </row>
@@ -21889,7 +23102,9 @@
       <c r="G547" s="3"/>
       <c r="H547" s="4"/>
       <c r="I547" s="4"/>
-      <c r="J547" s="7"/>
+      <c r="J547" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K547" s="8"/>
       <c r="L547" s="8"/>
     </row>
@@ -21917,7 +23132,9 @@
       <c r="I548" s="10" t="s">
         <v>1909</v>
       </c>
-      <c r="J548" s="7"/>
+      <c r="J548" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K548" s="8"/>
       <c r="L548" s="8"/>
     </row>
@@ -21943,7 +23160,9 @@
       <c r="G549" s="3"/>
       <c r="H549" s="4"/>
       <c r="I549" s="4"/>
-      <c r="J549" s="7"/>
+      <c r="J549" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K549" s="8"/>
       <c r="L549" s="8"/>
     </row>
@@ -21973,7 +23192,9 @@
         <v>1917</v>
       </c>
       <c r="I550" s="4"/>
-      <c r="J550" s="7"/>
+      <c r="J550" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K550" s="8"/>
       <c r="L550" s="8"/>
     </row>
@@ -21999,7 +23220,9 @@
       <c r="G551" s="3"/>
       <c r="H551" s="4"/>
       <c r="I551" s="4"/>
-      <c r="J551" s="7"/>
+      <c r="J551" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K551" s="8"/>
       <c r="L551" s="8"/>
     </row>
@@ -22025,7 +23248,9 @@
       <c r="G552" s="3"/>
       <c r="H552" s="4"/>
       <c r="I552" s="4"/>
-      <c r="J552" s="7"/>
+      <c r="J552" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K552" s="8"/>
       <c r="L552" s="8"/>
     </row>
@@ -22051,7 +23276,9 @@
       <c r="G553" s="3"/>
       <c r="H553" s="4"/>
       <c r="I553" s="4"/>
-      <c r="J553" s="7"/>
+      <c r="J553" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K553" s="8"/>
       <c r="L553" s="8"/>
     </row>
@@ -22077,7 +23304,9 @@
       <c r="G554" s="3"/>
       <c r="H554" s="4"/>
       <c r="I554" s="4"/>
-      <c r="J554" s="7"/>
+      <c r="J554" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K554" s="8"/>
       <c r="L554" s="8"/>
     </row>
@@ -22103,7 +23332,9 @@
       <c r="G555" s="3"/>
       <c r="H555" s="4"/>
       <c r="I555" s="4"/>
-      <c r="J555" s="7"/>
+      <c r="J555" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K555" s="8"/>
       <c r="L555" s="8"/>
     </row>
@@ -22129,7 +23360,9 @@
       <c r="G556" s="3"/>
       <c r="H556" s="4"/>
       <c r="I556" s="4"/>
-      <c r="J556" s="7"/>
+      <c r="J556" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K556" s="8"/>
       <c r="L556" s="8"/>
     </row>
@@ -22155,7 +23388,9 @@
       <c r="G557" s="3"/>
       <c r="H557" s="4"/>
       <c r="I557" s="4"/>
-      <c r="J557" s="7"/>
+      <c r="J557" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K557" s="8"/>
       <c r="L557" s="8"/>
     </row>
@@ -22179,7 +23414,9 @@
       <c r="G558" s="3"/>
       <c r="H558" s="4"/>
       <c r="I558" s="4"/>
-      <c r="J558" s="7"/>
+      <c r="J558" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K558" s="8"/>
       <c r="L558" s="8"/>
     </row>
@@ -22203,7 +23440,9 @@
       <c r="G559" s="3"/>
       <c r="H559" s="4"/>
       <c r="I559" s="4"/>
-      <c r="J559" s="7"/>
+      <c r="J559" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K559" s="8"/>
       <c r="L559" s="8"/>
     </row>
@@ -22229,7 +23468,9 @@
       <c r="G560" s="3"/>
       <c r="H560" s="4"/>
       <c r="I560" s="4"/>
-      <c r="J560" s="7"/>
+      <c r="J560" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K560" s="8"/>
       <c r="L560" s="8"/>
     </row>
@@ -22255,7 +23496,9 @@
       <c r="G561" s="3"/>
       <c r="H561" s="4"/>
       <c r="I561" s="4"/>
-      <c r="J561" s="7"/>
+      <c r="J561" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K561" s="8"/>
       <c r="L561" s="8"/>
     </row>
@@ -22281,7 +23524,9 @@
       <c r="G562" s="3"/>
       <c r="H562" s="4"/>
       <c r="I562" s="4"/>
-      <c r="J562" s="7"/>
+      <c r="J562" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K562" s="8"/>
       <c r="L562" s="8"/>
     </row>
@@ -22307,7 +23552,9 @@
       <c r="G563" s="3"/>
       <c r="H563" s="4"/>
       <c r="I563" s="4"/>
-      <c r="J563" s="7"/>
+      <c r="J563" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K563" s="8"/>
       <c r="L563" s="8"/>
     </row>
@@ -22333,7 +23580,9 @@
       <c r="G564" s="3"/>
       <c r="H564" s="4"/>
       <c r="I564" s="4"/>
-      <c r="J564" s="7"/>
+      <c r="J564" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K564" s="8"/>
       <c r="L564" s="8"/>
     </row>
@@ -22363,7 +23612,9 @@
         <v>1964</v>
       </c>
       <c r="I565" s="4"/>
-      <c r="J565" s="7"/>
+      <c r="J565" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K565" s="8"/>
       <c r="L565" s="8"/>
     </row>
@@ -22389,7 +23640,9 @@
       <c r="G566" s="3"/>
       <c r="H566" s="4"/>
       <c r="I566" s="4"/>
-      <c r="J566" s="7"/>
+      <c r="J566" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K566" s="8"/>
       <c r="L566" s="8"/>
     </row>
@@ -22415,7 +23668,9 @@
       <c r="G567" s="3"/>
       <c r="H567" s="4"/>
       <c r="I567" s="4"/>
-      <c r="J567" s="7"/>
+      <c r="J567" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K567" s="8"/>
       <c r="L567" s="8"/>
     </row>
@@ -22441,7 +23696,9 @@
       <c r="G568" s="3"/>
       <c r="H568" s="4"/>
       <c r="I568" s="4"/>
-      <c r="J568" s="7"/>
+      <c r="J568" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K568" s="8"/>
       <c r="L568" s="8"/>
     </row>
@@ -22467,7 +23724,9 @@
       <c r="G569" s="3"/>
       <c r="H569" s="4"/>
       <c r="I569" s="4"/>
-      <c r="J569" s="7"/>
+      <c r="J569" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K569" s="8"/>
       <c r="L569" s="8"/>
     </row>
@@ -22493,7 +23752,9 @@
       <c r="G570" s="3"/>
       <c r="H570" s="4"/>
       <c r="I570" s="4"/>
-      <c r="J570" s="7"/>
+      <c r="J570" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K570" s="8"/>
       <c r="L570" s="8"/>
     </row>
@@ -22523,7 +23784,9 @@
         <v>1983</v>
       </c>
       <c r="I571" s="4"/>
-      <c r="J571" s="7"/>
+      <c r="J571" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K571" s="8"/>
       <c r="L571" s="8"/>
     </row>
@@ -22547,7 +23810,9 @@
       <c r="G572" s="3"/>
       <c r="H572" s="4"/>
       <c r="I572" s="4"/>
-      <c r="J572" s="7"/>
+      <c r="J572" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K572" s="8"/>
       <c r="L572" s="8"/>
     </row>
@@ -22575,7 +23840,9 @@
         <v>24</v>
       </c>
       <c r="I573" s="4"/>
-      <c r="J573" s="7"/>
+      <c r="J573" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K573" s="8"/>
       <c r="L573" s="8"/>
     </row>
@@ -22605,7 +23872,9 @@
         <v>1284</v>
       </c>
       <c r="I574" s="4"/>
-      <c r="J574" s="7"/>
+      <c r="J574" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K574" s="8"/>
       <c r="L574" s="8"/>
     </row>
@@ -22629,7 +23898,9 @@
       <c r="G575" s="3"/>
       <c r="H575" s="4"/>
       <c r="I575" s="4"/>
-      <c r="J575" s="7"/>
+      <c r="J575" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K575" s="8"/>
       <c r="L575" s="8"/>
     </row>
@@ -22655,7 +23926,9 @@
       <c r="G576" s="3"/>
       <c r="H576" s="4"/>
       <c r="I576" s="4"/>
-      <c r="J576" s="7"/>
+      <c r="J576" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K576" s="8"/>
       <c r="L576" s="8"/>
     </row>
@@ -22685,7 +23958,9 @@
         <v>2002</v>
       </c>
       <c r="I577" s="4"/>
-      <c r="J577" s="7"/>
+      <c r="J577" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K577" s="8"/>
       <c r="L577" s="8"/>
     </row>
@@ -22711,7 +23986,9 @@
       <c r="G578" s="3"/>
       <c r="H578" s="4"/>
       <c r="I578" s="4"/>
-      <c r="J578" s="7"/>
+      <c r="J578" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K578" s="8"/>
       <c r="L578" s="8"/>
     </row>
@@ -22737,7 +24014,9 @@
       <c r="G579" s="3"/>
       <c r="H579" s="4"/>
       <c r="I579" s="4"/>
-      <c r="J579" s="7"/>
+      <c r="J579" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K579" s="8"/>
       <c r="L579" s="8"/>
     </row>
@@ -22763,7 +24042,9 @@
       <c r="G580" s="3"/>
       <c r="H580" s="4"/>
       <c r="I580" s="4"/>
-      <c r="J580" s="7"/>
+      <c r="J580" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K580" s="8"/>
       <c r="L580" s="8"/>
     </row>
@@ -22789,7 +24070,9 @@
         <v>24</v>
       </c>
       <c r="I581" s="4"/>
-      <c r="J581" s="7"/>
+      <c r="J581" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K581" s="8"/>
       <c r="L581" s="8"/>
     </row>
@@ -22819,7 +24102,9 @@
         <v>2020</v>
       </c>
       <c r="I582" s="4"/>
-      <c r="J582" s="7"/>
+      <c r="J582" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K582" s="8"/>
       <c r="L582" s="8"/>
     </row>
@@ -22845,7 +24130,9 @@
       <c r="G583" s="3"/>
       <c r="H583" s="4"/>
       <c r="I583" s="4"/>
-      <c r="J583" s="7"/>
+      <c r="J583" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K583" s="8"/>
       <c r="L583" s="8"/>
     </row>
@@ -22869,7 +24156,9 @@
       <c r="G584" s="3"/>
       <c r="H584" s="4"/>
       <c r="I584" s="4"/>
-      <c r="J584" s="7"/>
+      <c r="J584" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K584" s="8"/>
       <c r="L584" s="8"/>
     </row>
@@ -22897,7 +24186,9 @@
         <v>789</v>
       </c>
       <c r="I585" s="4"/>
-      <c r="J585" s="7"/>
+      <c r="J585" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K585" s="8"/>
       <c r="L585" s="8"/>
     </row>
@@ -22923,7 +24214,9 @@
       <c r="G586" s="3"/>
       <c r="H586" s="4"/>
       <c r="I586" s="4"/>
-      <c r="J586" s="7"/>
+      <c r="J586" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K586" s="8"/>
       <c r="L586" s="8"/>
     </row>
@@ -22949,7 +24242,9 @@
       <c r="G587" s="3"/>
       <c r="H587" s="4"/>
       <c r="I587" s="4"/>
-      <c r="J587" s="7"/>
+      <c r="J587" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K587" s="8"/>
       <c r="L587" s="8"/>
     </row>
@@ -22979,7 +24274,9 @@
         <v>2041</v>
       </c>
       <c r="I588" s="4"/>
-      <c r="J588" s="7"/>
+      <c r="J588" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K588" s="8"/>
       <c r="L588" s="8"/>
     </row>
@@ -23005,7 +24302,9 @@
       <c r="G589" s="3"/>
       <c r="H589" s="4"/>
       <c r="I589" s="4"/>
-      <c r="J589" s="7"/>
+      <c r="J589" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K589" s="8"/>
       <c r="L589" s="8"/>
     </row>
@@ -23031,7 +24330,9 @@
       <c r="G590" s="3"/>
       <c r="H590" s="4"/>
       <c r="I590" s="4"/>
-      <c r="J590" s="7"/>
+      <c r="J590" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K590" s="8"/>
       <c r="L590" s="8"/>
     </row>
@@ -23055,7 +24356,9 @@
       <c r="G591" s="3"/>
       <c r="H591" s="4"/>
       <c r="I591" s="4"/>
-      <c r="J591" s="7"/>
+      <c r="J591" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K591" s="8"/>
       <c r="L591" s="8"/>
     </row>
@@ -23083,7 +24386,9 @@
         <v>2054</v>
       </c>
       <c r="I592" s="4"/>
-      <c r="J592" s="7"/>
+      <c r="J592" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K592" s="8"/>
       <c r="L592" s="8"/>
     </row>
@@ -23109,7 +24414,9 @@
       <c r="G593" s="3"/>
       <c r="H593" s="4"/>
       <c r="I593" s="4"/>
-      <c r="J593" s="7"/>
+      <c r="J593" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K593" s="8"/>
       <c r="L593" s="8"/>
     </row>
@@ -23135,7 +24442,9 @@
       <c r="G594" s="3"/>
       <c r="H594" s="4"/>
       <c r="I594" s="4"/>
-      <c r="J594" s="7"/>
+      <c r="J594" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K594" s="8"/>
       <c r="L594" s="8"/>
     </row>
@@ -23165,7 +24474,9 @@
         <v>2066</v>
       </c>
       <c r="I595" s="4"/>
-      <c r="J595" s="7"/>
+      <c r="J595" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K595" s="8"/>
       <c r="L595" s="8"/>
     </row>
@@ -23191,7 +24502,9 @@
       <c r="G596" s="3"/>
       <c r="H596" s="4"/>
       <c r="I596" s="4"/>
-      <c r="J596" s="7"/>
+      <c r="J596" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K596" s="8"/>
       <c r="L596" s="8"/>
     </row>
@@ -23217,7 +24530,9 @@
       <c r="G597" s="3"/>
       <c r="H597" s="4"/>
       <c r="I597" s="4"/>
-      <c r="J597" s="7"/>
+      <c r="J597" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K597" s="8"/>
       <c r="L597" s="8"/>
     </row>
@@ -23243,7 +24558,9 @@
       <c r="G598" s="3"/>
       <c r="H598" s="4"/>
       <c r="I598" s="4"/>
-      <c r="J598" s="7"/>
+      <c r="J598" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K598" s="8"/>
       <c r="L598" s="8"/>
     </row>
@@ -23267,7 +24584,9 @@
       <c r="G599" s="3"/>
       <c r="H599" s="4"/>
       <c r="I599" s="4"/>
-      <c r="J599" s="7"/>
+      <c r="J599" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K599" s="8"/>
       <c r="L599" s="8"/>
     </row>
@@ -23293,7 +24612,9 @@
       <c r="G600" s="3"/>
       <c r="H600" s="4"/>
       <c r="I600" s="4"/>
-      <c r="J600" s="7"/>
+      <c r="J600" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K600" s="8"/>
       <c r="L600" s="8"/>
     </row>
@@ -23317,7 +24638,9 @@
       <c r="G601" s="3"/>
       <c r="H601" s="4"/>
       <c r="I601" s="4"/>
-      <c r="J601" s="7"/>
+      <c r="J601" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K601" s="8"/>
       <c r="L601" s="8"/>
     </row>
@@ -23343,7 +24666,9 @@
         <v>2089</v>
       </c>
       <c r="I602" s="4"/>
-      <c r="J602" s="7"/>
+      <c r="J602" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K602" s="8"/>
       <c r="L602" s="8"/>
     </row>
@@ -23367,7 +24692,9 @@
       <c r="G603" s="3"/>
       <c r="H603" s="4"/>
       <c r="I603" s="4"/>
-      <c r="J603" s="7"/>
+      <c r="J603" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K603" s="8"/>
       <c r="L603" s="8"/>
     </row>
@@ -23391,7 +24718,9 @@
       <c r="G604" s="3"/>
       <c r="H604" s="4"/>
       <c r="I604" s="4"/>
-      <c r="J604" s="7"/>
+      <c r="J604" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K604" s="8"/>
       <c r="L604" s="8"/>
     </row>
@@ -23415,7 +24744,9 @@
       <c r="G605" s="3"/>
       <c r="H605" s="4"/>
       <c r="I605" s="4"/>
-      <c r="J605" s="7"/>
+      <c r="J605" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K605" s="8"/>
       <c r="L605" s="8"/>
     </row>
@@ -23439,7 +24770,9 @@
       <c r="G606" s="3"/>
       <c r="H606" s="4"/>
       <c r="I606" s="4"/>
-      <c r="J606" s="7"/>
+      <c r="J606" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K606" s="8"/>
       <c r="L606" s="8"/>
     </row>
@@ -23463,7 +24796,9 @@
       <c r="G607" s="3"/>
       <c r="H607" s="4"/>
       <c r="I607" s="4"/>
-      <c r="J607" s="7"/>
+      <c r="J607" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K607" s="8"/>
       <c r="L607" s="8"/>
     </row>
@@ -23487,7 +24822,9 @@
       <c r="G608" s="3"/>
       <c r="H608" s="4"/>
       <c r="I608" s="4"/>
-      <c r="J608" s="7"/>
+      <c r="J608" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K608" s="8"/>
       <c r="L608" s="8"/>
     </row>
@@ -23511,7 +24848,9 @@
       <c r="G609" s="3"/>
       <c r="H609" s="4"/>
       <c r="I609" s="4"/>
-      <c r="J609" s="7"/>
+      <c r="J609" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K609" s="8"/>
       <c r="L609" s="8"/>
     </row>
@@ -23537,7 +24876,9 @@
       <c r="I610" s="10" t="s">
         <v>2111</v>
       </c>
-      <c r="J610" s="7"/>
+      <c r="J610" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K610" s="8"/>
       <c r="L610" s="8"/>
     </row>
@@ -23563,7 +24904,9 @@
         <v>2114</v>
       </c>
       <c r="I611" s="4"/>
-      <c r="J611" s="7"/>
+      <c r="J611" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K611" s="8"/>
       <c r="L611" s="8"/>
     </row>
@@ -23587,7 +24930,9 @@
       <c r="G612" s="3"/>
       <c r="H612" s="4"/>
       <c r="I612" s="4"/>
-      <c r="J612" s="7"/>
+      <c r="J612" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K612" s="8"/>
       <c r="L612" s="8"/>
     </row>
@@ -23613,7 +24958,9 @@
         <v>24</v>
       </c>
       <c r="I613" s="4"/>
-      <c r="J613" s="7"/>
+      <c r="J613" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K613" s="8"/>
       <c r="L613" s="8"/>
     </row>
@@ -23637,7 +24984,9 @@
       <c r="G614" s="3"/>
       <c r="H614" s="4"/>
       <c r="I614" s="4"/>
-      <c r="J614" s="7"/>
+      <c r="J614" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K614" s="8"/>
       <c r="L614" s="8"/>
     </row>
@@ -23665,8 +25014,12 @@
         <v>2127</v>
       </c>
       <c r="I615" s="4"/>
-      <c r="J615" s="7"/>
-      <c r="K615" s="8"/>
+      <c r="J615" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K615" s="8" t="s">
+        <v>2254</v>
+      </c>
       <c r="L615" s="8"/>
     </row>
     <row r="616" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
@@ -23691,8 +25044,12 @@
         <v>2131</v>
       </c>
       <c r="I616" s="4"/>
-      <c r="J616" s="7"/>
-      <c r="K616" s="8"/>
+      <c r="J616" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K616" s="8" t="s">
+        <v>2251</v>
+      </c>
       <c r="L616" s="8"/>
     </row>
     <row r="617" spans="1:12" x14ac:dyDescent="0.2">
@@ -23719,8 +25076,12 @@
         <v>2135</v>
       </c>
       <c r="I617" s="4"/>
-      <c r="J617" s="7"/>
-      <c r="K617" s="8"/>
+      <c r="J617" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K617" s="8" t="s">
+        <v>2252</v>
+      </c>
       <c r="L617" s="8"/>
     </row>
     <row r="618" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
@@ -23743,7 +25104,9 @@
       <c r="G618" s="3"/>
       <c r="H618" s="4"/>
       <c r="I618" s="4"/>
-      <c r="J618" s="7"/>
+      <c r="J618" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K618" s="8"/>
       <c r="L618" s="8"/>
     </row>
@@ -23769,8 +25132,12 @@
         <v>2142</v>
       </c>
       <c r="I619" s="4"/>
-      <c r="J619" s="7"/>
-      <c r="K619" s="8"/>
+      <c r="J619" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K619" s="8" t="s">
+        <v>2253</v>
+      </c>
       <c r="L619" s="8"/>
     </row>
     <row r="620" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
@@ -23799,7 +25166,9 @@
       <c r="I620" s="10" t="s">
         <v>2147</v>
       </c>
-      <c r="J620" s="7"/>
+      <c r="J620" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K620" s="8"/>
       <c r="L620" s="8"/>
     </row>
@@ -23825,7 +25194,9 @@
       <c r="I621" s="10" t="s">
         <v>2147</v>
       </c>
-      <c r="J621" s="7"/>
+      <c r="J621" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K621" s="8"/>
       <c r="L621" s="8"/>
     </row>
@@ -23851,7 +25222,9 @@
       <c r="I622" s="10" t="s">
         <v>2147</v>
       </c>
-      <c r="J622" s="7"/>
+      <c r="J622" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K622" s="8"/>
       <c r="L622" s="8"/>
     </row>
@@ -23877,7 +25250,9 @@
       <c r="I623" s="10" t="s">
         <v>2147</v>
       </c>
-      <c r="J623" s="7"/>
+      <c r="J623" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K623" s="8"/>
       <c r="L623" s="8"/>
     </row>
@@ -23903,7 +25278,9 @@
       <c r="I624" s="10" t="s">
         <v>2147</v>
       </c>
-      <c r="J624" s="7"/>
+      <c r="J624" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K624" s="8"/>
       <c r="L624" s="8"/>
     </row>
@@ -23929,7 +25306,9 @@
       <c r="I625" s="10" t="s">
         <v>2147</v>
       </c>
-      <c r="J625" s="7"/>
+      <c r="J625" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K625" s="8"/>
       <c r="L625" s="8"/>
     </row>
@@ -23955,7 +25334,9 @@
       <c r="I626" s="10" t="s">
         <v>2147</v>
       </c>
-      <c r="J626" s="7"/>
+      <c r="J626" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K626" s="8"/>
       <c r="L626" s="8"/>
     </row>
@@ -23981,7 +25362,9 @@
       <c r="I627" s="10" t="s">
         <v>2147</v>
       </c>
-      <c r="J627" s="7"/>
+      <c r="J627" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K627" s="8"/>
       <c r="L627" s="8"/>
     </row>
@@ -24007,7 +25390,9 @@
       <c r="I628" s="10" t="s">
         <v>2147</v>
       </c>
-      <c r="J628" s="7"/>
+      <c r="J628" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K628" s="8"/>
       <c r="L628" s="8"/>
     </row>
@@ -24033,7 +25418,9 @@
       <c r="I629" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="J629" s="7"/>
+      <c r="J629" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K629" s="8"/>
       <c r="L629" s="8"/>
     </row>
@@ -24059,7 +25446,9 @@
       <c r="I630" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="J630" s="7"/>
+      <c r="J630" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K630" s="8"/>
       <c r="L630" s="8"/>
     </row>
@@ -24085,7 +25474,9 @@
       <c r="I631" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="J631" s="7"/>
+      <c r="J631" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K631" s="8"/>
       <c r="L631" s="8"/>
     </row>
@@ -24111,7 +25502,9 @@
       <c r="I632" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="J632" s="7"/>
+      <c r="J632" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K632" s="8"/>
       <c r="L632" s="8"/>
     </row>
@@ -24137,7 +25530,9 @@
       <c r="I633" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="J633" s="7"/>
+      <c r="J633" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K633" s="8"/>
       <c r="L633" s="8"/>
     </row>
@@ -24163,7 +25558,9 @@
       <c r="I634" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="J634" s="7"/>
+      <c r="J634" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K634" s="8"/>
       <c r="L634" s="8"/>
     </row>
@@ -24189,7 +25586,9 @@
       <c r="I635" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="J635" s="7"/>
+      <c r="J635" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K635" s="8"/>
       <c r="L635" s="8"/>
     </row>
@@ -24215,7 +25614,9 @@
       <c r="I636" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="J636" s="7"/>
+      <c r="J636" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K636" s="8"/>
       <c r="L636" s="8"/>
     </row>
@@ -24241,7 +25642,9 @@
       <c r="I637" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="J637" s="7"/>
+      <c r="J637" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K637" s="8"/>
       <c r="L637" s="8"/>
     </row>
@@ -24267,7 +25670,9 @@
       <c r="I638" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="J638" s="7"/>
+      <c r="J638" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K638" s="8"/>
       <c r="L638" s="8"/>
     </row>
@@ -24293,7 +25698,9 @@
       <c r="I639" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="J639" s="7"/>
+      <c r="J639" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K639" s="8"/>
       <c r="L639" s="8"/>
     </row>
@@ -24319,7 +25726,9 @@
       <c r="I640" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="J640" s="7"/>
+      <c r="J640" s="7" t="s">
+        <v>2229</v>
+      </c>
       <c r="K640" s="8"/>
       <c r="L640" s="8"/>
     </row>
@@ -24347,8 +25756,12 @@
         <v>2212</v>
       </c>
       <c r="I641" s="4"/>
-      <c r="J641" s="7"/>
-      <c r="K641" s="8"/>
+      <c r="J641" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K641" s="8" t="s">
+        <v>2249</v>
+      </c>
       <c r="L641" s="8"/>
     </row>
     <row r="642" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
@@ -24371,8 +25784,12 @@
       <c r="G642" s="3"/>
       <c r="H642" s="4"/>
       <c r="I642" s="4"/>
-      <c r="J642" s="7"/>
-      <c r="K642" s="8"/>
+      <c r="J642" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K642" s="8" t="s">
+        <v>2250</v>
+      </c>
       <c r="L642" s="8"/>
     </row>
   </sheetData>
